--- a/tame_output/ON/bt/strategyON_20240610.xlsx
+++ b/tame_output/ON/bt/strategyON_20240610.xlsx
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898223</v>
+        <v>3.716991718982231</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509537</v>
+        <v>3.737026608509538</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760811</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
@@ -46671,7 +46671,7 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378101</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
@@ -46694,7 +46694,7 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131252</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
@@ -46717,7 +46717,7 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067867</v>
+        <v>3.722447362067868</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
@@ -46740,7 +46740,7 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789124</v>
+        <v>3.787425580789125</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
@@ -46763,7 +46763,7 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.78150125051991</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
@@ -46786,7 +46786,7 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181172</v>
+        <v>3.802245929181173</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
@@ -46855,7 +46855,7 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798428</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
@@ -47321,16 +47321,16 @@
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-5.413053840035344</v>
+        <v>-5.412988719108017</v>
       </c>
       <c r="E1990" t="n">
-        <v>0.7178002277933482</v>
+        <v>0.7178262761642791</v>
       </c>
       <c r="F1990" t="n">
-        <v>-0.6568531072372213</v>
+        <v>-0.6568791533348927</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.489266323778901</v>
+        <v>2.489250696120298</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240610.xlsx
+++ b/tame_output/ON/bt/strategyON_20240610.xlsx
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.3%</t>
+          <t>108.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.9%</t>
+          <t>-50.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.8%</t>
+          <t>-77.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.6%</t>
+          <t>453.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-702.9%</t>
+          <t>-701.3%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-26.5%</t>
+          <t>-26.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-304.4%</t>
+          <t>-303.8%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-32.9%</t>
+          <t>-33.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-27.1%</t>
+          <t>-27.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-289.7%</t>
+          <t>-291.0%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-197.1%</t>
+          <t>-197.9%</t>
         </is>
       </c>
     </row>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982231</v>
+        <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509538</v>
+        <v>3.737026608509537</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.702309454760811</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
@@ -46671,7 +46671,7 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.709510443378101</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
@@ -46694,7 +46694,7 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131252</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
@@ -46717,7 +46717,7 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067868</v>
+        <v>3.722447362067867</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
@@ -46740,7 +46740,7 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789125</v>
+        <v>3.787425580789124</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
@@ -46763,7 +46763,7 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.78150125051991</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
@@ -46786,7 +46786,7 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181173</v>
+        <v>3.802245929181172</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
@@ -46855,7 +46855,7 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798428</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
@@ -47321,16 +47321,16 @@
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-5.412988719108017</v>
+        <v>-5.39699692765842</v>
       </c>
       <c r="E1990" t="n">
-        <v>0.7178262761642791</v>
+        <v>0.7242229927441182</v>
       </c>
       <c r="F1990" t="n">
-        <v>-0.6568791533348927</v>
+        <v>-0.6698397166681622</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.489250696120298</v>
+        <v>2.481474358120336</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240610.xlsx
+++ b/tame_output/ON/bt/strategyON_20240610.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-81.1%</t>
+          <t>-80.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.2%</t>
+          <t>107.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.7%</t>
+          <t>126.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,12 +982,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.8%</t>
+          <t>-50.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.7%</t>
+          <t>-76.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>89.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.7%</t>
+          <t>454.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-701.3%</t>
+          <t>-679.6%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1140,22 +1140,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-39.1%</t>
+          <t>-41.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-26.6%</t>
+          <t>-26.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-9.9%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-303.8%</t>
+          <t>-295.1%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-33.1%</t>
+          <t>-30.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>70.1%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.6%</t>
+          <t>-34.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-27.3%</t>
+          <t>-23.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-154.4%</t>
+          <t>-156.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-291.0%</t>
+          <t>-268.2%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-197.9%</t>
+          <t>-184.2%</t>
         </is>
       </c>
     </row>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898223</v>
+        <v>3.716991718982231</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509537</v>
+        <v>3.737026608509538</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.326613810281574</v>
+        <v>-5.091732489672752</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.5665910384783261</v>
+        <v>0.6605435667218553</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.8436484351252611</v>
+        <v>-0.628068653468133</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.191403925829547</v>
+        <v>2.320751794823824</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760811</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.427811591718747</v>
+        <v>-5.192930271109924</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.5253158477999582</v>
+        <v>0.6192683760434874</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.9120572486705802</v>
+        <v>-0.6964774670134521</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.149562559598857</v>
+        <v>2.278910428593134</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.395336005547975</v>
+        <v>-5.160454684939152</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.535906043822584</v>
+        <v>0.6298585720661132</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.9120572486705802</v>
+        <v>-0.6964774670134521</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.147162521153174</v>
+        <v>2.27651039014745</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378101</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.376297877840678</v>
+        <v>-5.141416557231855</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.5400460141137478</v>
+        <v>0.6339985423572769</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.9702408600017748</v>
+        <v>-0.7546610783446467</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.108777073562702</v>
+        <v>2.238124942556979</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131252</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.407424508991296</v>
+        <v>-5.172543188382473</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.7051772305921808</v>
+        <v>0.79912975883571</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.9702408600017748</v>
+        <v>-0.7546610783446467</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.286358942501382</v>
+        <v>2.415706811495659</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067867</v>
+        <v>3.722447362067868</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.459744889592088</v>
+        <v>-5.224863568983265</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.685082407337998</v>
+        <v>0.7790349355815271</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.9352939999929026</v>
+        <v>-0.7197142183357745</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.308160387492839</v>
+        <v>2.437508256487116</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789124</v>
+        <v>3.787425580789125</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.480002188121046</v>
+        <v>-5.245120867512223</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.6829880183233406</v>
+        <v>0.7769405465668697</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.9352939999929026</v>
+        <v>-0.7197142183357745</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.314168917889765</v>
+        <v>2.443516786884042</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.78150125051991</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.332259217886043</v>
+        <v>-5.09737789727722</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.8212378542093637</v>
+        <v>0.9151903824528929</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.7674866427580195</v>
+        <v>-0.5519068611008914</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.494005980022717</v>
+        <v>2.623353849016994</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181172</v>
+        <v>3.802245929181173</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.434273900417264</v>
+        <v>-5.199392579808442</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.783225602728356</v>
+        <v>0.8771781309718851</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.7674866427580195</v>
+        <v>-0.5519068611008914</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.496799601554198</v>
+        <v>2.626147470548475</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.42812119436448</v>
+        <v>-5.193239873755657</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.7863490335411281</v>
+        <v>0.8803015617846572</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.7613339367052352</v>
+        <v>-0.5457541550481071</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.501153573577527</v>
+        <v>2.630501442571803</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.57088652718713</v>
+        <v>-5.336005206578307</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.7283233771521784</v>
+        <v>0.8222759053957076</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.9040992695278856</v>
+        <v>-0.6885194878707575</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.414574850624047</v>
+        <v>2.543922719618323</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798428</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.508588528411008</v>
+        <v>-5.273707207802185</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.8195781304594481</v>
+        <v>0.9135306587029772</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.9040992695278856</v>
+        <v>-0.6885194878707575</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.480910404420868</v>
+        <v>2.610258273415145</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-5.30679833074585</v>
+        <v>-5.071917010137027</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.6088750819149094</v>
+        <v>0.7028276101584385</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.7060810773587312</v>
+        <v>-0.4905012957016031</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.308302192111758</v>
+        <v>2.437650061106035</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-5.246907649103257</v>
+        <v>-5.012026328494434</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.7031215868941221</v>
+        <v>0.7970741151376508</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.6461903957161377</v>
+        <v>-0.4306106140590096</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.41452683341949</v>
+        <v>2.543874702413766</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.344648193728231</v>
+        <v>-5.109766873119408</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.6786531051601759</v>
+        <v>0.772605633403705</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.6620796738491179</v>
+        <v>-0.4464998921919898</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.419621002655745</v>
+        <v>2.548968871650022</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.52098595385116</v>
+        <v>-5.286104633242338</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.6066539819356755</v>
+        <v>0.7006065101792047</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.8384174339720474</v>
+        <v>-0.6228376523149192</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.312354327406659</v>
+        <v>2.441702196400936</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.520296581689937</v>
+        <v>-5.285415261081114</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.6054213488400935</v>
+        <v>0.6993738770836226</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.8384174339720474</v>
+        <v>-0.6228376523149192</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.310845945446588</v>
+        <v>2.440193814440865</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.52686754674453</v>
+        <v>-5.291986226135707</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.6026558302536928</v>
+        <v>0.6966083584972216</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.8449883990266402</v>
+        <v>-0.6294086173695121</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.306766233849268</v>
+        <v>2.436114102843545</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.518913576449758</v>
+        <v>-5.284032255840935</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.6058374183716015</v>
+        <v>0.6997899466151307</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.8449883990266402</v>
+        <v>-0.6294086173695121</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.306766233849268</v>
+        <v>2.436114102843545</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.508540200116671</v>
+        <v>-5.273658879507848</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.616368525932641</v>
+        <v>0.7103210541761702</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.8346150226935529</v>
+        <v>-0.6190352410364248</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.319372016676925</v>
+        <v>2.448719885671202</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-5.380855890322374</v>
+        <v>-5.145974569713552</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.6723346232250842</v>
+        <v>0.7662871514686134</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.7069307128992565</v>
+        <v>-0.4913509312421284</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.400874975928228</v>
+        <v>2.530222844922505</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.441522480724764</v>
+        <v>-5.206641160115941</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.6348226595400006</v>
+        <v>0.7287751877835298</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.7886290296177901</v>
+        <v>-0.573049247960662</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.33861065837298</v>
+        <v>2.467958527367257</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-5.376528620791118</v>
+        <v>-5.141647300182296</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.6649179061240873</v>
+        <v>0.7588704343676165</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.7617984150136348</v>
+        <v>-0.5462186333565067</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.358806729746102</v>
+        <v>2.488154598740378</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.477287256548117</v>
+        <v>-5.242405935939294</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.6287753914523662</v>
+        <v>0.7227279196958953</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.8506239837406402</v>
+        <v>-0.6350442020835121</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.309672328140977</v>
+        <v>2.439020197135253</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.433084419462216</v>
+        <v>-5.198203098853393</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.6523361288145635</v>
+        <v>0.7462886570580927</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.8064211466547397</v>
+        <v>-0.5908413649976116</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.342073632920354</v>
+        <v>2.471421501914631</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.470063447125659</v>
+        <v>-5.235182126516836</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.6359545182184339</v>
+        <v>0.729907046461963</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.7694472448634092</v>
+        <v>-0.5538674632062811</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.3626679744644</v>
+        <v>2.492015843458677</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.490121525990499</v>
+        <v>-5.255240205381677</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.6791790518555376</v>
+        <v>0.7731315800990664</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.7694472448634092</v>
+        <v>-0.5538674632062811</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.41391573964744</v>
+        <v>2.543263608641716</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-5.450190852812609</v>
+        <v>-5.215309532203786</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.6935920257209469</v>
+        <v>0.7875445539644756</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.7295165716855189</v>
+        <v>-0.5139367900283908</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.436314848148427</v>
+        <v>2.565662717142704</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-5.409720505249904</v>
+        <v>-5.174839184641082</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.7047283929842987</v>
+        <v>0.7986809212278279</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.6890462241228139</v>
+        <v>-0.4734664424656858</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.45554528492432</v>
+        <v>2.584893153918597</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-5.344496324122699</v>
+        <v>-5.109615003513876</v>
       </c>
       <c r="E1988" t="n">
-        <v>0.7480054695278859</v>
+        <v>0.8419579977714147</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.6238220429956083</v>
+        <v>-0.4082422613384802</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.511867197693348</v>
+        <v>2.641215066687625</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-5.394990614479755</v>
+        <v>-5.160109293870932</v>
       </c>
       <c r="E1989" t="n">
-        <v>0.7237687256843435</v>
+        <v>0.8177212539278726</v>
       </c>
       <c r="F1989" t="n">
-        <v>-0.6688427801216825</v>
+        <v>-0.4532629984645544</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.480815727716984</v>
+        <v>2.610163596711261</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.821468627434679</v>
+        <v>3.880788245947002</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-5.39699692765842</v>
+        <v>-5.180220949905641</v>
       </c>
       <c r="E1990" t="n">
-        <v>0.7242229927441182</v>
+        <v>0.8109333838452297</v>
       </c>
       <c r="F1990" t="n">
-        <v>-0.6698397166681622</v>
+        <v>-0.4422356534671352</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.481474358120336</v>
+        <v>2.618036796040952</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240610.xlsx
+++ b/tame_output/ON/bt/strategyON_20240610.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>61.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>54.1%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-23.3%</t>
+          <t>-21.3%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.2%</t>
+          <t>-81.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.7%</t>
+          <t>108.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>126.6%</t>
+          <t>127.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,12 +982,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.0%</t>
+          <t>-50.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.6%</t>
+          <t>-77.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.3%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.1%</t>
+          <t>453.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.3%</t>
+          <t>-10.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-679.6%</t>
+          <t>-701.3%</t>
         </is>
       </c>
     </row>
@@ -1074,26 +1074,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1140,22 +1140,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.8%</t>
+          <t>-39.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-26.9%</t>
+          <t>-25.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-295.1%</t>
+          <t>-303.8%</t>
         </is>
       </c>
     </row>
@@ -1232,26 +1232,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-30.0%</t>
+          <t>-33.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-34.4%</t>
+          <t>-32.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-23.9%</t>
+          <t>-27.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-156.5%</t>
+          <t>-155.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-268.2%</t>
+          <t>-291.0%</t>
         </is>
       </c>
     </row>
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,17 +1418,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-184.2%</t>
+          <t>-156.4%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1990"/>
+  <dimension ref="A1:G1991"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839724</v>
+        <v>3.833252747839723</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388727</v>
+        <v>3.839374447388726</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626472</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291811</v>
+        <v>3.78733042929181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.801637122785787</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390428</v>
+        <v>3.763182248390427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105952</v>
+        <v>3.784718794105951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960987</v>
+        <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607645</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710812</v>
+        <v>3.76033368671081</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409206</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.782922533493419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792047</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919908</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318094</v>
+        <v>3.748328408318092</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057527</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.8359579870115</v>
+        <v>3.835957987011498</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392989</v>
+        <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632783</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883075</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074784</v>
+        <v>3.798814771074782</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242294</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367686</v>
+        <v>3.821593509367684</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879967</v>
+        <v>3.822326997879966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861662650234</v>
+        <v>3.848616626502338</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.81866895167594</v>
+        <v>3.818668951675938</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539951</v>
+        <v>3.84327452753995</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496264</v>
+        <v>3.845047386496262</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942104</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674516</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430696</v>
+        <v>3.729146398430694</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003604</v>
+        <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508372</v>
+        <v>3.71417913950837</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417705</v>
+        <v>3.710906731417703</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205901</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225446</v>
+        <v>3.765024323225444</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111295</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264163</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316048</v>
+        <v>3.752027499316047</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809499</v>
+        <v>3.733390600809498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472739</v>
+        <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798538</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498866</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705326</v>
+        <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729271</v>
+        <v>3.68271631072927</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.73301244119077</v>
+        <v>3.733012441190769</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982231</v>
+        <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509538</v>
+        <v>3.737026608509537</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.091732489672752</v>
+        <v>-5.326613810281574</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.6605435667218553</v>
+        <v>0.5665910384783261</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.628068653468133</v>
+        <v>-0.8436484351252611</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.320751794823824</v>
+        <v>2.191403925829547</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.702309454760811</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.192930271109924</v>
+        <v>-5.427811591718747</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.6192683760434874</v>
+        <v>0.5253158477999582</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.6964774670134521</v>
+        <v>-0.9120572486705802</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.278910428593134</v>
+        <v>2.149562559598857</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.160454684939152</v>
+        <v>-5.395336005547975</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.6298585720661132</v>
+        <v>0.535906043822584</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.6964774670134521</v>
+        <v>-0.9120572486705802</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.27651039014745</v>
+        <v>2.147162521153174</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.709510443378101</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.141416557231855</v>
+        <v>-5.376297877840678</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.6339985423572769</v>
+        <v>0.5400460141137478</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.7546610783446467</v>
+        <v>-0.9702408600017748</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.238124942556979</v>
+        <v>2.108777073562702</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131252</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.172543188382473</v>
+        <v>-5.407424508991296</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.79912975883571</v>
+        <v>0.7051772305921808</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.7546610783446467</v>
+        <v>-0.9702408600017748</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.415706811495659</v>
+        <v>2.286358942501382</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067868</v>
+        <v>3.722447362067867</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.224863568983265</v>
+        <v>-5.459744889592088</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.7790349355815271</v>
+        <v>0.685082407337998</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.7197142183357745</v>
+        <v>-0.9352939999929026</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.437508256487116</v>
+        <v>2.308160387492839</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789125</v>
+        <v>3.787425580789124</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.245120867512223</v>
+        <v>-5.480002188121046</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.7769405465668697</v>
+        <v>0.6829880183233406</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.7197142183357745</v>
+        <v>-0.9352939999929026</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.443516786884042</v>
+        <v>2.314168917889765</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.78150125051991</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.09737789727722</v>
+        <v>-5.332259217886043</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9151903824528929</v>
+        <v>0.8212378542093637</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.5519068611008914</v>
+        <v>-0.7674866427580195</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.623353849016994</v>
+        <v>2.494005980022717</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181173</v>
+        <v>3.802245929181172</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.199392579808442</v>
+        <v>-5.434273900417264</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8771781309718851</v>
+        <v>0.783225602728356</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.5519068611008914</v>
+        <v>-0.7674866427580195</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.626147470548475</v>
+        <v>2.496799601554198</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.193239873755657</v>
+        <v>-5.42812119436448</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8803015617846572</v>
+        <v>0.7863490335411281</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.5457541550481071</v>
+        <v>-0.7613339367052352</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.630501442571803</v>
+        <v>2.501153573577527</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.336005206578307</v>
+        <v>-5.57088652718713</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8222759053957076</v>
+        <v>0.7283233771521784</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.6885194878707575</v>
+        <v>-0.9040992695278856</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.543922719618323</v>
+        <v>2.414574850624047</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798428</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.273707207802185</v>
+        <v>-5.508588528411008</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9135306587029772</v>
+        <v>0.8195781304594481</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.6885194878707575</v>
+        <v>-0.9040992695278856</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.610258273415145</v>
+        <v>2.480910404420868</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-5.071917010137027</v>
+        <v>-5.30679833074585</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.7028276101584385</v>
+        <v>0.6088750819149094</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.4905012957016031</v>
+        <v>-0.7060810773587312</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.437650061106035</v>
+        <v>2.308302192111758</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-5.012026328494434</v>
+        <v>-5.246907649103257</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.7970741151376508</v>
+        <v>0.7031215868941221</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.4306106140590096</v>
+        <v>-0.6461903957161377</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.543874702413766</v>
+        <v>2.41452683341949</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.109766873119408</v>
+        <v>-5.344648193728231</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.772605633403705</v>
+        <v>0.6786531051601759</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.4464998921919898</v>
+        <v>-0.6620796738491179</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.548968871650022</v>
+        <v>2.419621002655745</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.286104633242338</v>
+        <v>-5.52098595385116</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.7006065101792047</v>
+        <v>0.6066539819356755</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.6228376523149192</v>
+        <v>-0.8384174339720474</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.441702196400936</v>
+        <v>2.312354327406659</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.285415261081114</v>
+        <v>-5.520296581689937</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.6993738770836226</v>
+        <v>0.6054213488400935</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.6228376523149192</v>
+        <v>-0.8384174339720474</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.440193814440865</v>
+        <v>2.310845945446588</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.291986226135707</v>
+        <v>-5.52686754674453</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.6966083584972216</v>
+        <v>0.6026558302536928</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.6294086173695121</v>
+        <v>-0.8449883990266402</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.436114102843545</v>
+        <v>2.306766233849268</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.284032255840935</v>
+        <v>-5.518913576449758</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.6997899466151307</v>
+        <v>0.6058374183716015</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.6294086173695121</v>
+        <v>-0.8449883990266402</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.436114102843545</v>
+        <v>2.306766233849268</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.273658879507848</v>
+        <v>-5.508540200116671</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.7103210541761702</v>
+        <v>0.616368525932641</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.6190352410364248</v>
+        <v>-0.8346150226935529</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.448719885671202</v>
+        <v>2.319372016676925</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-5.145974569713552</v>
+        <v>-5.380855890322374</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.7662871514686134</v>
+        <v>0.6723346232250842</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.4913509312421284</v>
+        <v>-0.7069307128992565</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.530222844922505</v>
+        <v>2.400874975928228</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.206641160115941</v>
+        <v>-5.441522480724764</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.7287751877835298</v>
+        <v>0.6348226595400006</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.573049247960662</v>
+        <v>-0.7886290296177901</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.467958527367257</v>
+        <v>2.33861065837298</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-5.141647300182296</v>
+        <v>-5.376528620791118</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.7588704343676165</v>
+        <v>0.6649179061240873</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.5462186333565067</v>
+        <v>-0.7617984150136348</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.488154598740378</v>
+        <v>2.358806729746102</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.242405935939294</v>
+        <v>-5.477287256548117</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.7227279196958953</v>
+        <v>0.6287753914523662</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.6350442020835121</v>
+        <v>-0.8506239837406402</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.439020197135253</v>
+        <v>2.309672328140977</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.198203098853393</v>
+        <v>-5.433084419462216</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.7462886570580927</v>
+        <v>0.6523361288145635</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.5908413649976116</v>
+        <v>-0.8064211466547397</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.471421501914631</v>
+        <v>2.342073632920354</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.235182126516836</v>
+        <v>-5.470063447125659</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.729907046461963</v>
+        <v>0.6359545182184339</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.5538674632062811</v>
+        <v>-0.7694472448634092</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.492015843458677</v>
+        <v>2.3626679744644</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.255240205381677</v>
+        <v>-5.490121525990499</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.7731315800990664</v>
+        <v>0.6791790518555376</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.5538674632062811</v>
+        <v>-0.7694472448634092</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.543263608641716</v>
+        <v>2.41391573964744</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-5.215309532203786</v>
+        <v>-5.450190852812609</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.7875445539644756</v>
+        <v>0.6935920257209469</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.5139367900283908</v>
+        <v>-0.7295165716855189</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.565662717142704</v>
+        <v>2.436314848148427</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-5.174839184641082</v>
+        <v>-5.409720505249904</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.7986809212278279</v>
+        <v>0.7047283929842987</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.4734664424656858</v>
+        <v>-0.6890462241228139</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.584893153918597</v>
+        <v>2.45554528492432</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-5.109615003513876</v>
+        <v>-5.344496324122699</v>
       </c>
       <c r="E1988" t="n">
-        <v>0.8419579977714147</v>
+        <v>0.7480054695278859</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.4082422613384802</v>
+        <v>-0.6238220429956083</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.641215066687625</v>
+        <v>2.511867197693348</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-5.160109293870932</v>
+        <v>-5.394990614479755</v>
       </c>
       <c r="E1989" t="n">
-        <v>0.8177212539278726</v>
+        <v>0.7237687256843435</v>
       </c>
       <c r="F1989" t="n">
-        <v>-0.4532629984645544</v>
+        <v>-0.6688427801216825</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.610163596711261</v>
+        <v>2.480815727716984</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,45 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.880788245947002</v>
+        <v>3.845198842749918</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-5.180220949905641</v>
+        <v>-5.39699692765842</v>
       </c>
       <c r="E1990" t="n">
-        <v>0.8109333838452297</v>
+        <v>0.7242229927441182</v>
       </c>
       <c r="F1990" t="n">
-        <v>-0.4422356534671352</v>
+        <v>-0.6698397166681622</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.618036796040952</v>
+        <v>2.481474358120336</v>
+      </c>
+    </row>
+    <row r="1991">
+      <c r="A1991" s="2" t="n">
+        <v>45453</v>
+      </c>
+      <c r="B1991" t="n">
+        <v>3.821589239973433</v>
+      </c>
+      <c r="C1991" t="n">
+        <v>2.903176207674377</v>
+      </c>
+      <c r="D1991" t="n">
+        <v>-5.39699692765842</v>
+      </c>
+      <c r="E1991" t="n">
+        <v>0.7242229927441182</v>
+      </c>
+      <c r="F1991" t="n">
+        <v>-0.6698397166681622</v>
+      </c>
+      <c r="G1991" t="n">
+        <v>2.896240004660745</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240610.xlsx
+++ b/tame_output/ON/bt/strategyON_20240610.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-21.3%</t>
+          <t>-3.8%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-81.1%</t>
+          <t>-80.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.2%</t>
+          <t>107.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.6%</t>
+          <t>126.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,12 +982,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.8%</t>
+          <t>-50.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.7%</t>
+          <t>-76.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>89.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.3%</t>
+          <t>454.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.4%</t>
+          <t>-10.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-701.3%</t>
+          <t>-677.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1140,22 +1140,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-39.1%</t>
+          <t>-41.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-25.4%</t>
+          <t>-26.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-9.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-303.8%</t>
+          <t>-294.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-33.1%</t>
+          <t>-30.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>69.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.6%</t>
+          <t>-34.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-27.3%</t>
+          <t>-24.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.6%</t>
+          <t>-156.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-291.0%</t>
+          <t>-269.2%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>48.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-156.4%</t>
+          <t>-138.9%</t>
         </is>
       </c>
     </row>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898223</v>
+        <v>3.716991718982231</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509537</v>
+        <v>3.737026608509538</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.326613810281574</v>
+        <v>-5.087788069759561</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.5665910384783261</v>
+        <v>0.6621213346871317</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.8436484351252611</v>
+        <v>-0.6258580716678147</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.191403925829547</v>
+        <v>2.322078143904015</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760811</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.427811591718747</v>
+        <v>-5.188985851196733</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.5253158477999582</v>
+        <v>0.6208461440087638</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.9120572486705802</v>
+        <v>-0.694266885213134</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.149562559598857</v>
+        <v>2.280236777673324</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.395336005547975</v>
+        <v>-5.156510265025961</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.535906043822584</v>
+        <v>0.6314363400313896</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.9120572486705802</v>
+        <v>-0.694266885213134</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.147162521153174</v>
+        <v>2.277836739227641</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378101</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.376297877840678</v>
+        <v>-5.137472137318664</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.5400460141137478</v>
+        <v>0.6355763103225534</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.9702408600017748</v>
+        <v>-0.7524504965443285</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.108777073562702</v>
+        <v>2.239451291637169</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131252</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.407424508991296</v>
+        <v>-5.168598768469282</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.7051772305921808</v>
+        <v>0.8007075268009864</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.9702408600017748</v>
+        <v>-0.7524504965443285</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.286358942501382</v>
+        <v>2.41703316057585</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067867</v>
+        <v>3.722447362067868</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.459744889592088</v>
+        <v>-5.220919149070074</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.685082407337998</v>
+        <v>0.7806127035468036</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.9352939999929026</v>
+        <v>-0.7175036365354563</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.308160387492839</v>
+        <v>2.438834605567307</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789124</v>
+        <v>3.787425580789125</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.480002188121046</v>
+        <v>-5.241176447599032</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.6829880183233406</v>
+        <v>0.7785183145321461</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.9352939999929026</v>
+        <v>-0.7175036365354563</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.314168917889765</v>
+        <v>2.444843135964233</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.78150125051991</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.332259217886043</v>
+        <v>-5.093433477364029</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.8212378542093637</v>
+        <v>0.9167681504181693</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.7674866427580195</v>
+        <v>-0.5496962793005732</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.494005980022717</v>
+        <v>2.624680198097185</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181172</v>
+        <v>3.802245929181173</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.434273900417264</v>
+        <v>-5.195448159895251</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.783225602728356</v>
+        <v>0.8787558989371616</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.7674866427580195</v>
+        <v>-0.5496962793005732</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.496799601554198</v>
+        <v>2.627473819628666</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.42812119436448</v>
+        <v>-5.189295453842466</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.7863490335411281</v>
+        <v>0.8818793297499337</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.7613339367052352</v>
+        <v>-0.5435435732477889</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.501153573577527</v>
+        <v>2.631827791651995</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.57088652718713</v>
+        <v>-5.332060786665116</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.7283233771521784</v>
+        <v>0.823853673360984</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.9040992695278856</v>
+        <v>-0.6863089060704393</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.414574850624047</v>
+        <v>2.545249068698515</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798428</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.508588528411008</v>
+        <v>-5.269762787888994</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.8195781304594481</v>
+        <v>0.9151084266682536</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.9040992695278856</v>
+        <v>-0.6863089060704393</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.480910404420868</v>
+        <v>2.611584622495335</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-5.30679833074585</v>
+        <v>-5.067972590223836</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.6088750819149094</v>
+        <v>0.704405378123715</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.7060810773587312</v>
+        <v>-0.4882907139012849</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.308302192111758</v>
+        <v>2.438976410186226</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-5.246907649103257</v>
+        <v>-5.008081908581243</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.7031215868941221</v>
+        <v>0.7986518831029275</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.6461903957161377</v>
+        <v>-0.4284000322586914</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.41452683341949</v>
+        <v>2.545201051493958</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.344648193728231</v>
+        <v>-5.105822453206217</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.6786531051601759</v>
+        <v>0.7741834013689814</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.6620796738491179</v>
+        <v>-0.4442893103916716</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.419621002655745</v>
+        <v>2.550295220730213</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.52098595385116</v>
+        <v>-5.282160213329147</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.6066539819356755</v>
+        <v>0.7021842781444811</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.8384174339720474</v>
+        <v>-0.620627070514601</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.312354327406659</v>
+        <v>2.443028545481127</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.520296581689937</v>
+        <v>-5.281470841167923</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.6054213488400935</v>
+        <v>0.7009516450488991</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.8384174339720474</v>
+        <v>-0.620627070514601</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.310845945446588</v>
+        <v>2.441520163521055</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.52686754674453</v>
+        <v>-5.288041806222516</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.6026558302536928</v>
+        <v>0.698186126462498</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.8449883990266402</v>
+        <v>-0.627198035569194</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.306766233849268</v>
+        <v>2.437440451923736</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.518913576449758</v>
+        <v>-5.280087835927744</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.6058374183716015</v>
+        <v>0.7013677145804071</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.8449883990266402</v>
+        <v>-0.627198035569194</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.306766233849268</v>
+        <v>2.437440451923736</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.508540200116671</v>
+        <v>-5.269714459594657</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.616368525932641</v>
+        <v>0.7118988221414466</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.8346150226935529</v>
+        <v>-0.6168246592361066</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.319372016676925</v>
+        <v>2.450046234751393</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-5.380855890322374</v>
+        <v>-5.142030149800361</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.6723346232250842</v>
+        <v>0.7678649194338898</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.7069307128992565</v>
+        <v>-0.4891403494418102</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.400874975928228</v>
+        <v>2.531549194002696</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.441522480724764</v>
+        <v>-5.20269674020275</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.6348226595400006</v>
+        <v>0.7303529557488062</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.7886290296177901</v>
+        <v>-0.5708386661603438</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.33861065837298</v>
+        <v>2.469284876447448</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-5.376528620791118</v>
+        <v>-5.137702880269105</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.6649179061240873</v>
+        <v>0.7604482023328929</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.7617984150136348</v>
+        <v>-0.5440080515561885</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.358806729746102</v>
+        <v>2.48948094782057</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.477287256548117</v>
+        <v>-5.238461516026103</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.6287753914523662</v>
+        <v>0.7243056876611718</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.8506239837406402</v>
+        <v>-0.6328336202831939</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.309672328140977</v>
+        <v>2.440346546215444</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.433084419462216</v>
+        <v>-5.194258678940202</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.6523361288145635</v>
+        <v>0.7478664250233691</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.8064211466547397</v>
+        <v>-0.5886307831972935</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.342073632920354</v>
+        <v>2.472747850994822</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.470063447125659</v>
+        <v>-5.231237706603645</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.6359545182184339</v>
+        <v>0.7314848144272394</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.7694472448634092</v>
+        <v>-0.5516568814059629</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.3626679744644</v>
+        <v>2.493342192538868</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.490121525990499</v>
+        <v>-5.251295785468486</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.6791790518555376</v>
+        <v>0.7747093480643428</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.7694472448634092</v>
+        <v>-0.5516568814059629</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.41391573964744</v>
+        <v>2.544589957721907</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-5.450190852812609</v>
+        <v>-5.211365112290595</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.6935920257209469</v>
+        <v>0.7891223219297521</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.7295165716855189</v>
+        <v>-0.5117262082280726</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.436314848148427</v>
+        <v>2.566989066222895</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-5.409720505249904</v>
+        <v>-5.17089476472789</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.7047283929842987</v>
+        <v>0.8002586891931043</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.6890462241228139</v>
+        <v>-0.4712558606653676</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.45554528492432</v>
+        <v>2.586219502998787</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-5.344496324122699</v>
+        <v>-5.105670583600685</v>
       </c>
       <c r="E1988" t="n">
-        <v>0.7480054695278859</v>
+        <v>0.8435357657366911</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.6238220429956083</v>
+        <v>-0.406031679538162</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.511867197693348</v>
+        <v>2.642541415767816</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-5.394990614479755</v>
+        <v>-5.156164873957741</v>
       </c>
       <c r="E1989" t="n">
-        <v>0.7237687256843435</v>
+        <v>0.8192990218931491</v>
       </c>
       <c r="F1989" t="n">
-        <v>-0.6688427801216825</v>
+        <v>-0.4510524166642362</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.480815727716984</v>
+        <v>2.611489945791452</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-5.39699692765842</v>
+        <v>-5.158171187136406</v>
       </c>
       <c r="E1990" t="n">
-        <v>0.7242229927441182</v>
+        <v>0.8197532889529233</v>
       </c>
       <c r="F1990" t="n">
-        <v>-0.6698397166681622</v>
+        <v>-0.452049353210716</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.481474358120336</v>
+        <v>2.612148576194804</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.821589239973433</v>
+        <v>3.880607357227058</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.903176207674377</v>
+        <v>3.077983665845218</v>
       </c>
       <c r="D1991" t="n">
-        <v>-5.39699692765842</v>
+        <v>-5.158171187136406</v>
       </c>
       <c r="E1991" t="n">
-        <v>0.7242229927441182</v>
+        <v>0.8197532889529233</v>
       </c>
       <c r="F1991" t="n">
-        <v>-0.6698397166681622</v>
+        <v>-0.452049353210716</v>
       </c>
       <c r="G1991" t="n">
-        <v>2.896240004660745</v>
+        <v>3.071047462831586</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240610.xlsx
+++ b/tame_output/ON/bt/strategyON_20240610.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>28.1%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-30.9%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.1%</t>
+          <t>-81.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.6%</t>
+          <t>108.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>126.6%</t>
+          <t>127.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>86.9%</t>
+          <t>86.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,12 +982,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.0%</t>
+          <t>-50.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.5%</t>
+          <t>-78.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.3%</t>
+          <t>89.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.2%</t>
+          <t>450.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.3%</t>
+          <t>-10.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-677.4%</t>
+          <t>-705.1%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,22 +1140,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.8%</t>
+          <t>-39.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-26.9%</t>
+          <t>-21.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-9.4%</t>
+          <t>-28.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-294.2%</t>
+          <t>-305.3%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-30.1%</t>
+          <t>-33.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-34.4%</t>
+          <t>-32.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-24.0%</t>
+          <t>-28.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-156.3%</t>
+          <t>-156.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-269.2%</t>
+          <t>-294.5%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-138.9%</t>
+          <t>-166.0%</t>
         </is>
       </c>
     </row>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839723</v>
+        <v>3.833252747839724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.03025505039227</v>
+        <v>-8.933529377200253</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.460998470367401</v>
+        <v>-0.4223082010905941</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.414153261387922</v>
+        <v>-2.317427588195906</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.702968017270502</v>
+        <v>1.761003421185712</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.950185254854466</v>
+        <v>-8.853459581662449</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.4296037309315222</v>
+        <v>-0.3909134616547156</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.334083465850118</v>
+        <v>-2.237357792658102</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.750376715813941</v>
+        <v>1.808412119729151</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.716704032624868</v>
+        <v>-8.619978359432849</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.3282868132018306</v>
+        <v>-0.2895965439250232</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.100602243620519</v>
+        <v>-2.003876570428503</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.898389877989553</v>
+        <v>1.956425281904762</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.567037641617354</v>
+        <v>-8.470311968425335</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.2713124671117844</v>
+        <v>-0.232622197834977</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.007698752377983</v>
+        <v>-1.910973079185967</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.951239762422115</v>
+        <v>2.009275166337325</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.434762167986467</v>
+        <v>-8.338036494794448</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.2230347909124024</v>
+        <v>-0.184344521635595</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.875423278747097</v>
+        <v>-1.77869760555508</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.025972533347674</v>
+        <v>2.084007937262884</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.244162493313313</v>
+        <v>-8.147436820121294</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.143979860355504</v>
+        <v>-0.1052895910786966</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.684823604073944</v>
+        <v>-1.588097930881928</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.143147398839202</v>
+        <v>2.201182802754412</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.995162694629732</v>
+        <v>-7.898437021437713</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.03147359965841323</v>
+        <v>0.007216669618394622</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.684823604073944</v>
+        <v>-1.588097930881928</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.156053740062861</v>
+        <v>2.214089143978071</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.100752684402837</v>
+        <v>-8.004027011210818</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2016855251668734</v>
+        <v>-0.162995255890066</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.790413593847048</v>
+        <v>-1.693687920655032</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.96472381659978</v>
+        <v>2.02275922051499</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.119487586521434</v>
+        <v>-8.022761913329415</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1606351441372258</v>
+        <v>-0.1219448748604184</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.79600960350718</v>
+        <v>-1.699283930315163</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.009910552680787</v>
+        <v>2.067945956595997</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.971547545113834</v>
+        <v>-7.874821871921815</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.2213380502623536</v>
+        <v>-0.1826477809855462</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.775688687598622</v>
+        <v>-1.678963014406606</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.902224179537755</v>
+        <v>1.960259583452964</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.95438939498254</v>
+        <v>-7.857663721790521</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.2231887764633145</v>
+        <v>-0.1844985071865066</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.758530537467328</v>
+        <v>-1.661804864275311</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.903805083363053</v>
+        <v>1.961840487278263</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.91084098821185</v>
+        <v>-7.814115315019831</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.2127300258501315</v>
+        <v>-0.1740397565733236</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.758530537467328</v>
+        <v>-1.661804864275311</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.89684447126796</v>
+        <v>1.95487987518317</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.668692594757991</v>
+        <v>-7.571966921565973</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1014083140874451</v>
+        <v>-0.06271804481063725</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.758530537467328</v>
+        <v>-1.661804864275311</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.911306825649103</v>
+        <v>1.969342229564313</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.56043345763547</v>
+        <v>-7.463707784443451</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.06357253877924141</v>
+        <v>-0.02488226950243355</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.758530537467328</v>
+        <v>-1.661804864275311</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.905838946108298</v>
+        <v>1.963874350023508</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.437142322818339</v>
+        <v>-7.34041664962632</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.01675799084181184</v>
+        <v>0.02193227843499557</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.635239402650197</v>
+        <v>-1.538513729458181</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.977311721009153</v>
+        <v>2.035347124924363</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.415993123914896</v>
+        <v>-7.319267450722877</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.0005973330431094936</v>
+        <v>0.03809293623369792</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.614090203746754</v>
+        <v>-1.517364530554738</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.997702218588544</v>
+        <v>2.055737622503754</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.172227681931451</v>
+        <v>-7.075502008739432</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.09268955209731899</v>
+        <v>0.1313798213741264</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.614090203746754</v>
+        <v>-1.517364530554738</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.993482926935595</v>
+        <v>2.051518330850804</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.070464861654156</v>
+        <v>-6.973739188462138</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1355189941282529</v>
+        <v>0.1742092634050603</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.600871135354325</v>
+        <v>-1.504145462162309</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.003538681891068</v>
+        <v>2.061574085806278</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.820614467705082</v>
+        <v>-6.723888794513063</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2282012266915849</v>
+        <v>0.2668914959683923</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.600871135354325</v>
+        <v>-1.504145462162309</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.99628075687477</v>
+        <v>2.05431616078998</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.644722375237649</v>
+        <v>-6.54799670204563</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3021571871992066</v>
+        <v>0.3408474564760144</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.600871135354325</v>
+        <v>-1.504145462162309</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.999879880395419</v>
+        <v>2.057915284310629</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.473275912215185</v>
+        <v>-6.376550239023167</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.384063278462746</v>
+        <v>0.4227535477395534</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.429424672331862</v>
+        <v>-1.332698999139846</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.116075264263451</v>
+        <v>2.17411066817866</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.248242912546362</v>
+        <v>-6.151517239354344</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4730969559465721</v>
+        <v>0.5117872252233795</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.204391672663039</v>
+        <v>-1.107665999471023</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.250115541681041</v>
+        <v>2.308150945596251</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.184607170312428</v>
+        <v>-6.087881497120409</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.503246053894463</v>
+        <v>0.5419363231712704</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.140755930429105</v>
+        <v>-1.044030257237088</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.292991788075719</v>
+        <v>2.351027191990929</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.140844989006586</v>
+        <v>-6.044119315814568</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5019451852005954</v>
+        <v>0.5406354544774028</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.140755930429105</v>
+        <v>-1.044030257237088</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.274186046859515</v>
+        <v>2.332221450774725</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.900414492201726</v>
+        <v>-5.803688819009707</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5998604605474167</v>
+        <v>0.6385507298242246</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.9003254336242443</v>
+        <v>-0.803599760432228</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.420187421567308</v>
+        <v>2.478222825482518</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.828171924030531</v>
+        <v>-5.731446250838513</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6326868016507148</v>
+        <v>0.6713770709275226</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.9003254336242443</v>
+        <v>-0.803599760432228</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.424116735402129</v>
+        <v>2.482152139317338</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.775173601749144</v>
+        <v>-5.678447928557125</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6545647144806099</v>
+        <v>0.6932549837574178</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.8449891746223055</v>
+        <v>-0.7482635014302892</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.457997074720632</v>
+        <v>2.516032478635842</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.666368716269417</v>
+        <v>-5.569643043077398</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.6950847398924944</v>
+        <v>0.7337750091693018</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.8449891746223055</v>
+        <v>-0.7482635014302892</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.454995145940625</v>
+        <v>2.513030549855835</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.446347918232406</v>
+        <v>-5.466445958717051</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.7846720961179128</v>
+        <v>0.7766328799240547</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.7037693295543253</v>
+        <v>-0.7515242386483407</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.541306089992028</v>
+        <v>2.512653144535618</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.313480229169128</v>
+        <v>-5.333578269653773</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.853713354545047</v>
+        <v>0.845674138351189</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.7037693295543253</v>
+        <v>-0.7515242386483407</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.557200272793851</v>
+        <v>2.528547327337442</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.153965125649759</v>
+        <v>-5.174063166134403</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9186652403930968</v>
+        <v>0.9106260241992388</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.5442542260349553</v>
+        <v>-0.5920091351289708</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.654055179345775</v>
+        <v>2.625402233889365</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-5.009292980550021</v>
+        <v>-5.029391021034666</v>
       </c>
       <c r="E1932" t="n">
-        <v>0.9866222009944319</v>
+        <v>0.9785829848005738</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3995820809352179</v>
+        <v>-0.4473369900292334</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.750946568967057</v>
+        <v>2.722293623510648</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-5.069167807907713</v>
+        <v>-5.089265848392358</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9487097614527809</v>
+        <v>0.9406705452589228</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.45945690829291</v>
+        <v>-0.5072118173869256</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.701059163953868</v>
+        <v>2.672406218497458</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.982368310128704</v>
+        <v>-5.00246635061335</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.00583005388695</v>
+        <v>0.9977908376930922</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.45945690829291</v>
+        <v>-0.5072118173869256</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.723459657276434</v>
+        <v>2.694806711820025</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.98483801659051</v>
+        <v>-5.004936057075156</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.00491457267564</v>
+        <v>0.9968753564817818</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.4619266147547162</v>
+        <v>-0.5096815238487318</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.722050234772762</v>
+        <v>2.693397289316353</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-5.05320820291452</v>
+        <v>-5.073306243399166</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.9885734206207379</v>
+        <v>0.9805342044268799</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.5004058248125168</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.738622576669193</v>
+        <v>2.709969631212784</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.161746383830654</v>
+        <v>-5.1818444243153</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9355948568861758</v>
+        <v>0.9275556406923173</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.5004058248125168</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.729059285301084</v>
+        <v>2.700406339844675</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.19273954315936</v>
+        <v>-5.212837583644006</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.7479071581950807</v>
+        <v>0.7398679420012222</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.5004058248125168</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.553768850341471</v>
+        <v>2.525115904885062</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-5.017265283366891</v>
+        <v>-5.037363323851537</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.8226640941038559</v>
+        <v>0.8146248779099974</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.5004058248125168</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.558336082333259</v>
+        <v>2.52968313687685</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-5.12820153600814</v>
+        <v>-5.148299576492786</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.7540316218085632</v>
+        <v>0.7459924056147051</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.5004058248125168</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.534078111094466</v>
+        <v>2.505425165638057</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.331228113551373</v>
+        <v>-5.351326154036019</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.6759523760111756</v>
+        <v>0.6679131598173171</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.6556774932617346</v>
+        <v>-0.7034324023557502</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.415393549788432</v>
+        <v>2.386740604332022</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-5.17330251461608</v>
+        <v>-5.193400555100726</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.7492950020174249</v>
+        <v>0.7412557858235669</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.6556774932617346</v>
+        <v>-0.7034324023557502</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.425565936220564</v>
+        <v>2.396912990764155</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-5.087059051589702</v>
+        <v>-5.107157092074348</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.7787386578018367</v>
+        <v>0.7706994416079782</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.6556774932617346</v>
+        <v>-0.7034324023557502</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.420512206794424</v>
+        <v>2.391859261338015</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.132365870988682</v>
+        <v>-5.152463911473328</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.7523917054867701</v>
+        <v>0.7443524892929116</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.6964876562709654</v>
+        <v>-0.744242565364981</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.387801884433411</v>
+        <v>2.359148938977002</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-5.161398975690983</v>
+        <v>-5.181497016175629</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.7413303366389514</v>
+        <v>0.7332911204450929</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.6964876562709654</v>
+        <v>-0.744242565364981</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.388353757466513</v>
+        <v>2.359700812010104</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-5.068588494240124</v>
+        <v>-5.088686534724769</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.7077272211106607</v>
+        <v>0.6996880049168026</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.6036771748201061</v>
+        <v>-0.6514320839141217</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.373312738228394</v>
+        <v>2.344659792771985</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-5.112977963569551</v>
+        <v>-5.133076004054197</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.6918449093034904</v>
+        <v>0.6838056931096324</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.6480666441495337</v>
+        <v>-0.6958215532435493</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.348552532555338</v>
+        <v>2.319899587098929</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-5.000306745333301</v>
+        <v>-5.020404785817947</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.7319891051097136</v>
+        <v>0.7239498889158553</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.5353954259132836</v>
+        <v>-0.5831503350072992</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.411230972008811</v>
+        <v>2.382578026552402</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.887929744150628</v>
+        <v>-4.908027784635274</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.78243120141345</v>
+        <v>0.7743919852195917</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.5353954259132836</v>
+        <v>-0.5831503350072992</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.416722267839479</v>
+        <v>2.388069322383069</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-5.086164313037359</v>
+        <v>-5.106262353522005</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.7146345756272967</v>
+        <v>0.7065953594334387</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.7336299948000142</v>
+        <v>-0.7813849038940298</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.309278728275979</v>
+        <v>2.28062578281957</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-5.169165594062638</v>
+        <v>-5.189263634547284</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.5197897832178384</v>
+        <v>0.5117505670239804</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.7522008793271879</v>
+        <v>-0.7999557884212035</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.136491917560329</v>
+        <v>2.107838972103919</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.277779672505969</v>
+        <v>-5.297877712990615</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.5964938125597117</v>
+        <v>0.5884545963658532</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.7522008793271879</v>
+        <v>-0.7999557884212035</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.256641578279534</v>
+        <v>2.227988632823125</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.364378255487072</v>
+        <v>-5.384476295971718</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.5763674054695933</v>
+        <v>0.5683281892757353</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.7522008793271879</v>
+        <v>-0.7999557884212035</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.271154604381857</v>
+        <v>2.242501658925448</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.325994592928921</v>
+        <v>-5.346092633413567</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.5891403118352225</v>
+        <v>0.5811010956413645</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.7138172167690368</v>
+        <v>-0.7615721258630523</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.291604243259116</v>
+        <v>2.262951297802707</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-5.148878262893755</v>
+        <v>-5.1689763033784</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.656715872694591</v>
+        <v>0.6486766565007325</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.7138172167690368</v>
+        <v>-0.7615721258630523</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.288333272104418</v>
+        <v>2.259680326648009</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-5.1939705077273</v>
+        <v>-5.214068548211946</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.6393623665230859</v>
+        <v>0.6313231503292274</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.7757132599384265</v>
+        <v>-0.8234681690324421</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.251879037964698</v>
+        <v>2.223226092508289</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-5.014595086488533</v>
+        <v>-5.034693126973179</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.7048995103250073</v>
+        <v>0.6968602941311488</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.6189365017677079</v>
+        <v>-0.6666914108617235</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.339732068173543</v>
+        <v>2.311079122717134</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-5.059609300009139</v>
+        <v>-5.079707340493785</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.6677012802483544</v>
+        <v>0.6596620640544959</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.6492853970823125</v>
+        <v>-0.6970403061763281</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.30233018631637</v>
+        <v>2.273677240859961</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.087788069759561</v>
+        <v>-5.34671185076622</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.6621213346871317</v>
+        <v>0.5585518222844676</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.6258580716678147</v>
+        <v>-0.8914033442192767</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.322078143904015</v>
+        <v>2.162750980373137</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.188985851196733</v>
+        <v>-5.447909632203393</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.6208461440087638</v>
+        <v>0.5172766316061002</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.694266885213134</v>
+        <v>-0.9598121577645958</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.280236777673324</v>
+        <v>2.120909614142447</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.156510265025961</v>
+        <v>-5.415434046032621</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.6314363400313896</v>
+        <v>0.5278668276287255</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.694266885213134</v>
+        <v>-0.9598121577645958</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.277836739227641</v>
+        <v>2.118509575696764</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.137472137318664</v>
+        <v>-5.396395918325323</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.6355763103225534</v>
+        <v>0.5320067979198897</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.7524504965443285</v>
+        <v>-1.01799576909579</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.239451291637169</v>
+        <v>2.080124128106292</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.168598768469282</v>
+        <v>-5.427522549475942</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8007075268009864</v>
+        <v>0.6971380143983228</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.7524504965443285</v>
+        <v>-1.01799576909579</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.41703316057585</v>
+        <v>2.257705997044973</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.220919149070074</v>
+        <v>-5.479842930076734</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.7806127035468036</v>
+        <v>0.6770431911441395</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.7175036365354563</v>
+        <v>-0.983048909086918</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.438834605567307</v>
+        <v>2.27950744203643</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.241176447599032</v>
+        <v>-5.500100228605691</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.7785183145321461</v>
+        <v>0.6749488021294825</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.7175036365354563</v>
+        <v>-0.983048909086918</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.444843135964233</v>
+        <v>2.285515972433356</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.093433477364029</v>
+        <v>-5.352357258370689</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9167681504181693</v>
+        <v>0.8131986380155052</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.5496962793005732</v>
+        <v>-0.8152415518520348</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.624680198097185</v>
+        <v>2.465353034566307</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.195448159895251</v>
+        <v>-5.45437194090191</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8787558989371616</v>
+        <v>0.7751863865344979</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.5496962793005732</v>
+        <v>-0.8152415518520348</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.627473819628666</v>
+        <v>2.468146656097788</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.189295453842466</v>
+        <v>-5.448219234849126</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8818793297499337</v>
+        <v>0.77830981734727</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.5435435732477889</v>
+        <v>-0.8090888457992506</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.631827791651995</v>
+        <v>2.472500628121117</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.332060786665116</v>
+        <v>-5.590984567671776</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.823853673360984</v>
+        <v>0.7202841609583199</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.6863089060704393</v>
+        <v>-0.951854178621901</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.545249068698515</v>
+        <v>2.385921905167637</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.269762787888994</v>
+        <v>-5.528686568895654</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9151084266682536</v>
+        <v>0.81153891426559</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.6863089060704393</v>
+        <v>-0.951854178621901</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.611584622495335</v>
+        <v>2.452257458964458</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-5.067972590223836</v>
+        <v>-5.326896371230496</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.704405378123715</v>
+        <v>0.6008358657210509</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.4882907139012849</v>
+        <v>-0.7538359864527466</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.438976410186226</v>
+        <v>2.279649246655349</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-5.008081908581243</v>
+        <v>-5.267005689587902</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.7986518831029275</v>
+        <v>0.6950823707002636</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.4284000322586914</v>
+        <v>-0.6939453048101532</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.545201051493958</v>
+        <v>2.38587388796308</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.105822453206217</v>
+        <v>-5.364746234212877</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.7741834013689814</v>
+        <v>0.6706138889663174</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.4442893103916716</v>
+        <v>-0.7098345829431334</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.550295220730213</v>
+        <v>2.390968057199336</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.282160213329147</v>
+        <v>-5.541083994335806</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.7021842781444811</v>
+        <v>0.5986147657418175</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.620627070514601</v>
+        <v>-0.8861723430660629</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.443028545481127</v>
+        <v>2.28370138195025</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.281470841167923</v>
+        <v>-5.540394622174583</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.7009516450488991</v>
+        <v>0.5973821326462354</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.620627070514601</v>
+        <v>-0.8861723430660629</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.441520163521055</v>
+        <v>2.282192999990178</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.288041806222516</v>
+        <v>-5.546965587229176</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.698186126462498</v>
+        <v>0.5946166140598343</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.627198035569194</v>
+        <v>-0.8927433081206557</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.437440451923736</v>
+        <v>2.278113288392859</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.280087835927744</v>
+        <v>-5.539011616934403</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.7013677145804071</v>
+        <v>0.597798202177743</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.627198035569194</v>
+        <v>-0.8927433081206557</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.437440451923736</v>
+        <v>2.278113288392859</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.269714459594657</v>
+        <v>-5.528638240601317</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.7118988221414466</v>
+        <v>0.6083293097387825</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.6168246592361066</v>
+        <v>-0.8823699317875684</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.450046234751393</v>
+        <v>2.290719071220516</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-5.142030149800361</v>
+        <v>-5.40095393080702</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.7678649194338898</v>
+        <v>0.6642954070312261</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.4891403494418102</v>
+        <v>-0.7546856219932719</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.531549194002696</v>
+        <v>2.372222030471819</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.20269674020275</v>
+        <v>-5.46162052120941</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.7303529557488062</v>
+        <v>0.6267834433461426</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.5708386661603438</v>
+        <v>-0.8363839387118056</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.469284876447448</v>
+        <v>2.30995771291657</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-5.137702880269105</v>
+        <v>-5.396626661275764</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.7604482023328929</v>
+        <v>0.6568786899302292</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.5440080515561885</v>
+        <v>-0.8095533241076502</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.48948094782057</v>
+        <v>2.330153784289692</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.238461516026103</v>
+        <v>-5.497385297032762</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.7243056876611718</v>
+        <v>0.6207361752585081</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.6328336202831939</v>
+        <v>-0.8983788928346557</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.440346546215444</v>
+        <v>2.281019382684567</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.194258678940202</v>
+        <v>-5.453182459946862</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.7478664250233691</v>
+        <v>0.6442969126207054</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.5886307831972935</v>
+        <v>-0.8541760557487552</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.472747850994822</v>
+        <v>2.313420687463944</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.231237706603645</v>
+        <v>-5.490161487610305</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.7314848144272394</v>
+        <v>0.6279153020245758</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.5516568814059629</v>
+        <v>-0.8172021539574247</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.493342192538868</v>
+        <v>2.33401502900799</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.251295785468486</v>
+        <v>-5.510219566475145</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.7747093480643428</v>
+        <v>0.6711398356616791</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.5516568814059629</v>
+        <v>-0.8172021539574247</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.544589957721907</v>
+        <v>2.38526279419103</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-5.211365112290595</v>
+        <v>-5.470288893297255</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.7891223219297521</v>
+        <v>0.6855528095270884</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.5117262082280726</v>
+        <v>-0.7772714807795343</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.566989066222895</v>
+        <v>2.407661902692017</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-5.17089476472789</v>
+        <v>-5.42981854573455</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.8002586891931043</v>
+        <v>0.6966891767904402</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.4712558606653676</v>
+        <v>-0.7368011332168294</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.586219502998787</v>
+        <v>2.42689233946791</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-5.105670583600685</v>
+        <v>-5.364594364607345</v>
       </c>
       <c r="E1988" t="n">
-        <v>0.8435357657366911</v>
+        <v>0.7399662533340274</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.406031679538162</v>
+        <v>-0.6715769520896238</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.642541415767816</v>
+        <v>2.483214252236939</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-5.156164873957741</v>
+        <v>-5.415088654964401</v>
       </c>
       <c r="E1989" t="n">
-        <v>0.8192990218931491</v>
+        <v>0.7157295094904854</v>
       </c>
       <c r="F1989" t="n">
-        <v>-0.4510524166642362</v>
+        <v>-0.716597689215698</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.611489945791452</v>
+        <v>2.452162782260574</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-5.158171187136406</v>
+        <v>-5.435200310999109</v>
       </c>
       <c r="E1990" t="n">
-        <v>0.8197532889529233</v>
+        <v>0.7089416394078425</v>
       </c>
       <c r="F1990" t="n">
-        <v>-0.452049353210716</v>
+        <v>-0.7055703442182788</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.612148576194804</v>
+        <v>2.460035981590266</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.880607357227058</v>
+        <v>3.562265146267067</v>
       </c>
       <c r="C1991" t="n">
-        <v>3.077983665845218</v>
+        <v>2.807331855895701</v>
       </c>
       <c r="D1991" t="n">
-        <v>-5.158171187136406</v>
+        <v>-5.435200310999109</v>
       </c>
       <c r="E1991" t="n">
-        <v>0.8197532889529233</v>
+        <v>0.7089416394078425</v>
       </c>
       <c r="F1991" t="n">
-        <v>-0.452049353210716</v>
+        <v>-0.7055703442182788</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.071047462831586</v>
+        <v>2.800395652882069</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240610.xlsx
+++ b/tame_output/ON/bt/strategyON_20240610.xlsx
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,27 +839,27 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-30.9%</t>
+          <t>-39.9%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-81.2%</t>
+          <t>-81.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.1%</t>
+          <t>107.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>86.5%</t>
+          <t>86.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-78.2%</t>
+          <t>-78.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.6%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>450.0%</t>
+          <t>449.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-705.1%</t>
+          <t>-714.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-6.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-21.1%</t>
+          <t>-24.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-28.0%</t>
+          <t>-9.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-305.3%</t>
+          <t>-309.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-33.5%</t>
+          <t>-34.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-28.4%</t>
+          <t>-29.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-156.2%</t>
+          <t>-156.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-294.5%</t>
+          <t>-304.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-16.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-166.0%</t>
+          <t>-175.0%</t>
         </is>
       </c>
     </row>
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.933529377200253</v>
+        <v>-9.03025505039227</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.4223082010905941</v>
+        <v>-0.460998470367401</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.317427588195906</v>
+        <v>-2.414153261387922</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.761003421185712</v>
+        <v>1.702968017270502</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.853459581662449</v>
+        <v>-8.950185254854466</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.3909134616547156</v>
+        <v>-0.4296037309315222</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.237357792658102</v>
+        <v>-2.334083465850118</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.808412119729151</v>
+        <v>1.750376715813941</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.619978359432849</v>
+        <v>-8.716704032624868</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.2895965439250232</v>
+        <v>-0.3282868132018306</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.003876570428503</v>
+        <v>-2.100602243620519</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.956425281904762</v>
+        <v>1.898389877989553</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.470311968425335</v>
+        <v>-8.567037641617354</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.232622197834977</v>
+        <v>-0.2713124671117844</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.910973079185967</v>
+        <v>-2.007698752377983</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.009275166337325</v>
+        <v>1.951239762422115</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.338036494794448</v>
+        <v>-8.434762167986467</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.184344521635595</v>
+        <v>-0.2230347909124024</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.77869760555508</v>
+        <v>-1.875423278747097</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.084007937262884</v>
+        <v>2.025972533347674</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.147436820121294</v>
+        <v>-8.244162493313313</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.1052895910786966</v>
+        <v>-0.143979860355504</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.588097930881928</v>
+        <v>-1.684823604073944</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.201182802754412</v>
+        <v>2.143147398839202</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.898437021437713</v>
+        <v>-7.995162694629732</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.007216669618394622</v>
+        <v>-0.03147359965841323</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.588097930881928</v>
+        <v>-1.684823604073944</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.214089143978071</v>
+        <v>2.156053740062861</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.004027011210818</v>
+        <v>-8.100752684402837</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.162995255890066</v>
+        <v>-0.2016855251668734</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.693687920655032</v>
+        <v>-1.790413593847048</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.02275922051499</v>
+        <v>1.96472381659978</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.022761913329415</v>
+        <v>-8.119487586521434</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1219448748604184</v>
+        <v>-0.1606351441372258</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.699283930315163</v>
+        <v>-1.79600960350718</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.067945956595997</v>
+        <v>2.009910552680787</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.874821871921815</v>
+        <v>-7.971547545113834</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1826477809855462</v>
+        <v>-0.2213380502623536</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.678963014406606</v>
+        <v>-1.775688687598622</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.960259583452964</v>
+        <v>1.902224179537755</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.857663721790521</v>
+        <v>-7.95438939498254</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1844985071865066</v>
+        <v>-0.2231887764633145</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.661804864275311</v>
+        <v>-1.758530537467328</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.961840487278263</v>
+        <v>1.903805083363053</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.814115315019831</v>
+        <v>-7.91084098821185</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1740397565733236</v>
+        <v>-0.2127300258501315</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.661804864275311</v>
+        <v>-1.758530537467328</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.95487987518317</v>
+        <v>1.89684447126796</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.571966921565973</v>
+        <v>-7.668692594757991</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.06271804481063725</v>
+        <v>-0.1014083140874451</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.661804864275311</v>
+        <v>-1.758530537467328</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.969342229564313</v>
+        <v>1.911306825649103</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.463707784443451</v>
+        <v>-7.56043345763547</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.02488226950243355</v>
+        <v>-0.06357253877924141</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.661804864275311</v>
+        <v>-1.758530537467328</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.963874350023508</v>
+        <v>1.905838946108298</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.34041664962632</v>
+        <v>-7.437142322818339</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.02193227843499557</v>
+        <v>-0.01675799084181184</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.538513729458181</v>
+        <v>-1.635239402650197</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.035347124924363</v>
+        <v>1.977311721009153</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.319267450722877</v>
+        <v>-7.415993123914896</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.03809293623369792</v>
+        <v>-0.0005973330431094936</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.517364530554738</v>
+        <v>-1.614090203746754</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.055737622503754</v>
+        <v>1.997702218588544</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.075502008739432</v>
+        <v>-7.172227681931451</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1313798213741264</v>
+        <v>0.09268955209731899</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.517364530554738</v>
+        <v>-1.614090203746754</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.051518330850804</v>
+        <v>1.993482926935595</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.973739188462138</v>
+        <v>-7.070464861654156</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1742092634050603</v>
+        <v>0.1355189941282529</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.504145462162309</v>
+        <v>-1.600871135354325</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.061574085806278</v>
+        <v>2.003538681891068</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.723888794513063</v>
+        <v>-6.820614467705082</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2668914959683923</v>
+        <v>0.2282012266915849</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.504145462162309</v>
+        <v>-1.600871135354325</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.05431616078998</v>
+        <v>1.99628075687477</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.54799670204563</v>
+        <v>-6.644722375237649</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3408474564760144</v>
+        <v>0.3021571871992066</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.504145462162309</v>
+        <v>-1.600871135354325</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.057915284310629</v>
+        <v>1.999879880395419</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.376550239023167</v>
+        <v>-6.473275912215185</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4227535477395534</v>
+        <v>0.384063278462746</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.332698999139846</v>
+        <v>-1.429424672331862</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.17411066817866</v>
+        <v>2.116075264263451</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.151517239354344</v>
+        <v>-6.248242912546362</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5117872252233795</v>
+        <v>0.4730969559465721</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.107665999471023</v>
+        <v>-1.204391672663039</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.308150945596251</v>
+        <v>2.250115541681041</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.087881497120409</v>
+        <v>-6.184607170312428</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5419363231712704</v>
+        <v>0.503246053894463</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.044030257237088</v>
+        <v>-1.140755930429105</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.351027191990929</v>
+        <v>2.292991788075719</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.044119315814568</v>
+        <v>-6.140844989006586</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5406354544774028</v>
+        <v>0.5019451852005954</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.044030257237088</v>
+        <v>-1.140755930429105</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.332221450774725</v>
+        <v>2.274186046859515</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.803688819009707</v>
+        <v>-5.900414492201726</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6385507298242246</v>
+        <v>0.5998604605474167</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.803599760432228</v>
+        <v>-0.9003254336242443</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.478222825482518</v>
+        <v>2.420187421567308</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.731446250838513</v>
+        <v>-5.828171924030531</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6713770709275226</v>
+        <v>0.6326868016507148</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.803599760432228</v>
+        <v>-0.9003254336242443</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.482152139317338</v>
+        <v>2.424116735402129</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.678447928557125</v>
+        <v>-5.775173601749144</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6932549837574178</v>
+        <v>0.6545647144806099</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7482635014302892</v>
+        <v>-0.8449891746223055</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.516032478635842</v>
+        <v>2.457997074720632</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502338</v>
+        <v>3.848616626502339</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.569643043077398</v>
+        <v>-5.666368716269417</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7337750091693018</v>
+        <v>0.6950847398924944</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7482635014302892</v>
+        <v>-0.8449891746223055</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.513030549855835</v>
+        <v>2.454995145940625</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.466445958717051</v>
+        <v>-5.562786607879484</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.7766328799240547</v>
+        <v>0.7380966202590815</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.7515242386483407</v>
+        <v>-0.8474496195133334</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.512653144535618</v>
+        <v>2.455097916016623</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.333578269653773</v>
+        <v>-5.429918918816206</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.845674138351189</v>
+        <v>0.8071378786862162</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.7515242386483407</v>
+        <v>-0.8474496195133334</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.528547327337442</v>
+        <v>2.470992098818446</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.174063166134403</v>
+        <v>-5.270403815296836</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9106260241992388</v>
+        <v>0.872089764534266</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.5920091351289708</v>
+        <v>-0.6879345159939635</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.625402233889365</v>
+        <v>2.56784700537037</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-5.029391021034666</v>
+        <v>-5.125731670197099</v>
       </c>
       <c r="E1932" t="n">
-        <v>0.9785829848005738</v>
+        <v>0.9400467251356006</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.4473369900292334</v>
+        <v>-0.5432623708942261</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.722293623510648</v>
+        <v>2.664738394991652</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-5.089265848392358</v>
+        <v>-5.185606497554791</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9406705452589228</v>
+        <v>0.9021342855939496</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.5072118173869256</v>
+        <v>-0.6031371982519182</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.672406218497458</v>
+        <v>2.614850989978463</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-5.00246635061335</v>
+        <v>-5.098806999775782</v>
       </c>
       <c r="E1934" t="n">
-        <v>0.9977908376930922</v>
+        <v>0.9592545780281192</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.5072118173869256</v>
+        <v>-0.6031371982519182</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.694806711820025</v>
+        <v>2.637251483301029</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-5.004936057075156</v>
+        <v>-5.101276706237588</v>
       </c>
       <c r="E1935" t="n">
-        <v>0.9968753564817818</v>
+        <v>0.9583390968168093</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.5096815238487318</v>
+        <v>-0.6056069047137245</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.693397289316353</v>
+        <v>2.635842060797357</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-5.073306243399166</v>
+        <v>-5.169646892561598</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.9805342044268799</v>
+        <v>0.9419979447619071</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.5004058248125168</v>
+        <v>-0.5963312056775095</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.709969631212784</v>
+        <v>2.652414402693788</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.1818444243153</v>
+        <v>-5.278185073477732</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9275556406923173</v>
+        <v>0.8890193810273446</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.5004058248125168</v>
+        <v>-0.5963312056775095</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.700406339844675</v>
+        <v>2.64285111132568</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.212837583644006</v>
+        <v>-5.309178232806437</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.7398679420012222</v>
+        <v>0.7013316823362494</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.5004058248125168</v>
+        <v>-0.5963312056775095</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.525115904885062</v>
+        <v>2.467560676366066</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-5.037363323851537</v>
+        <v>-5.133703973013969</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.8146248779099974</v>
+        <v>0.7760886182450246</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.5004058248125168</v>
+        <v>-0.5963312056775095</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.52968313687685</v>
+        <v>2.472127908357854</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-5.148299576492786</v>
+        <v>-5.244640225655218</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.7459924056147051</v>
+        <v>0.7074561459497324</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.5004058248125168</v>
+        <v>-0.5963312056775095</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.505425165638057</v>
+        <v>2.447869937119061</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.351326154036019</v>
+        <v>-5.447666803198451</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.6679131598173171</v>
+        <v>0.6293769001523444</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.7034324023557502</v>
+        <v>-0.7993577832207429</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.386740604332022</v>
+        <v>2.329185375813027</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-5.193400555100726</v>
+        <v>-5.289741204263158</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.7412557858235669</v>
+        <v>0.7027195261585941</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.7034324023557502</v>
+        <v>-0.7993577832207429</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.396912990764155</v>
+        <v>2.339357762245159</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-5.107157092074348</v>
+        <v>-5.20349774123678</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.7706994416079782</v>
+        <v>0.7321631819430054</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.7034324023557502</v>
+        <v>-0.7993577832207429</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.391859261338015</v>
+        <v>2.334304032819019</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.152463911473328</v>
+        <v>-5.24880456063576</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.7443524892929116</v>
+        <v>0.7058162296279389</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.744242565364981</v>
+        <v>-0.8401679462299737</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.359148938977002</v>
+        <v>2.301593710458007</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-5.181497016175629</v>
+        <v>-5.277837665338061</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.7332911204450929</v>
+        <v>0.6947548607801202</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.744242565364981</v>
+        <v>-0.8401679462299737</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.359700812010104</v>
+        <v>2.302145583491108</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-5.088686534724769</v>
+        <v>-5.185027183887201</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.6996880049168026</v>
+        <v>0.6611517452518298</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.6514320839141217</v>
+        <v>-0.7473574647791144</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.344659792771985</v>
+        <v>2.287104564252989</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-5.133076004054197</v>
+        <v>-5.229416653216629</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.6838056931096324</v>
+        <v>0.6452694334446596</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.6958215532435493</v>
+        <v>-0.791746934108542</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.319899587098929</v>
+        <v>2.262344358579933</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-5.020404785817947</v>
+        <v>-5.116745434980379</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.7239498889158553</v>
+        <v>0.6854136292508826</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.5831503350072992</v>
+        <v>-0.6790757158722918</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.382578026552402</v>
+        <v>2.325022798033407</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.908027784635274</v>
+        <v>-5.004368433797706</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.7743919852195917</v>
+        <v>0.735855725554619</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.5831503350072992</v>
+        <v>-0.6790757158722918</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.388069322383069</v>
+        <v>2.330514093864074</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-5.106262353522005</v>
+        <v>-5.202603002684437</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.7065953594334387</v>
+        <v>0.6680590997684659</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.7813849038940298</v>
+        <v>-0.8773102847590224</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.28062578281957</v>
+        <v>2.223070554300575</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-5.189263634547284</v>
+        <v>-5.285604283709715</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.5117505670239804</v>
+        <v>0.4732143073590076</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.7999557884212035</v>
+        <v>-0.8958811692861961</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.107838972103919</v>
+        <v>2.050283743584924</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.297877712990615</v>
+        <v>-5.394218362153047</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.5884545963658532</v>
+        <v>0.5499183367008804</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.7999557884212035</v>
+        <v>-0.8958811692861961</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.227988632823125</v>
+        <v>2.170433404304129</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.384476295971718</v>
+        <v>-5.48081694513415</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.5683281892757353</v>
+        <v>0.5297919296107625</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.7999557884212035</v>
+        <v>-0.8958811692861961</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.242501658925448</v>
+        <v>2.184946430406452</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.346092633413567</v>
+        <v>-5.442433282575998</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.5811010956413645</v>
+        <v>0.5425648359763917</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.7615721258630523</v>
+        <v>-0.8574975067280449</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.262951297802707</v>
+        <v>2.205396069283712</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-5.1689763033784</v>
+        <v>-5.265316952540832</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.6486766565007325</v>
+        <v>0.6101403968357597</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.7615721258630523</v>
+        <v>-0.8574975067280449</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.259680326648009</v>
+        <v>2.202125098129013</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-5.214068548211946</v>
+        <v>-5.310409197374378</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.6313231503292274</v>
+        <v>0.5927868906642546</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.8234681690324421</v>
+        <v>-0.9193935498974347</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.223226092508289</v>
+        <v>2.165670863989293</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-5.034693126973179</v>
+        <v>-5.13103377613561</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.6968602941311488</v>
+        <v>0.658324034466176</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.6666914108617235</v>
+        <v>-0.762616791726716</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.311079122717134</v>
+        <v>2.253523894198138</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-5.079707340493785</v>
+        <v>-5.176047989656217</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.6596620640544959</v>
+        <v>0.6211258043895231</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.6970403061763281</v>
+        <v>-0.7929656870413206</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.273677240859961</v>
+        <v>2.216122012340966</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.34671185076622</v>
+        <v>-5.443052499928652</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.5585518222844676</v>
+        <v>0.5200155626194949</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.8914033442192767</v>
+        <v>-0.9873287250842693</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.162750980373137</v>
+        <v>2.105195751854142</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.447909632203393</v>
+        <v>-5.544250281365825</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.5172766316061002</v>
+        <v>0.4787403719411274</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.9598121577645958</v>
+        <v>-1.055737538629588</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.120909614142447</v>
+        <v>2.063354385623452</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.415434046032621</v>
+        <v>-5.511774695195053</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.5278668276287255</v>
+        <v>0.4893305679637527</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.9598121577645958</v>
+        <v>-1.055737538629588</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.118509575696764</v>
+        <v>2.060954347177768</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.396395918325323</v>
+        <v>-5.492736567487755</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.5320067979198897</v>
+        <v>0.4934705382549169</v>
       </c>
       <c r="F1962" t="n">
-        <v>-1.01799576909579</v>
+        <v>-1.113921149960783</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.080124128106292</v>
+        <v>2.022568899587297</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.427522549475942</v>
+        <v>-5.523863198638374</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.6971380143983228</v>
+        <v>0.65860175473335</v>
       </c>
       <c r="F1963" t="n">
-        <v>-1.01799576909579</v>
+        <v>-1.113921149960783</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.257705997044973</v>
+        <v>2.200150768525977</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.479842930076734</v>
+        <v>-5.576183579239165</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.6770431911441395</v>
+        <v>0.6385069314791667</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.983048909086918</v>
+        <v>-1.078974289951911</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.27950744203643</v>
+        <v>2.221952213517434</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.500100228605691</v>
+        <v>-5.596440877768123</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.6749488021294825</v>
+        <v>0.6364125424645097</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.983048909086918</v>
+        <v>-1.078974289951911</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.285515972433356</v>
+        <v>2.22796074391436</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.352357258370689</v>
+        <v>-5.448697907533121</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.8131986380155052</v>
+        <v>0.7746623783505324</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.8152415518520348</v>
+        <v>-0.9111669327170276</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.465353034566307</v>
+        <v>2.407797806047312</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.45437194090191</v>
+        <v>-5.550712590064342</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.7751863865344979</v>
+        <v>0.7366501268695251</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.8152415518520348</v>
+        <v>-0.9111669327170276</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.468146656097788</v>
+        <v>2.410591427578793</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.448219234849126</v>
+        <v>-5.544559884011558</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.77830981734727</v>
+        <v>0.7397735576822972</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.8090888457992506</v>
+        <v>-0.9050142266642434</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.472500628121117</v>
+        <v>2.414945399602122</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.590984567671776</v>
+        <v>-5.687325216834208</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.7202841609583199</v>
+        <v>0.6817479012933472</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.951854178621901</v>
+        <v>-1.047779559486894</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.385921905167637</v>
+        <v>2.328366676648642</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.528686568895654</v>
+        <v>-5.625027218058086</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.81153891426559</v>
+        <v>0.7730026546006172</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.951854178621901</v>
+        <v>-1.047779559486894</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.452257458964458</v>
+        <v>2.394702230445463</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-5.326896371230496</v>
+        <v>-5.423237020392928</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.6008358657210509</v>
+        <v>0.5622996060560781</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.7538359864527466</v>
+        <v>-0.8497613673177393</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.279649246655349</v>
+        <v>2.222094018136354</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-5.267005689587902</v>
+        <v>-5.363346338750334</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.6950823707002636</v>
+        <v>0.6565461110352908</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.6939453048101532</v>
+        <v>-0.7898706856751458</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.38587388796308</v>
+        <v>2.328318659444085</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.364746234212877</v>
+        <v>-5.461086883375309</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.6706138889663174</v>
+        <v>0.6320776293013446</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.7098345829431334</v>
+        <v>-0.8057599638081261</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.390968057199336</v>
+        <v>2.33341282868034</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.541083994335806</v>
+        <v>-5.637424643498238</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.5986147657418175</v>
+        <v>0.5600785060768447</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.8861723430660629</v>
+        <v>-0.9820977239310555</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.28370138195025</v>
+        <v>2.226146153431254</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.540394622174583</v>
+        <v>-5.636735271337015</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.5973821326462354</v>
+        <v>0.5588458729812626</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.8861723430660629</v>
+        <v>-0.9820977239310555</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.282192999990178</v>
+        <v>2.224637771471183</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.546965587229176</v>
+        <v>-5.643306236391608</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.5946166140598343</v>
+        <v>0.5560803543948616</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.8927433081206557</v>
+        <v>-0.9886686889856484</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.278113288392859</v>
+        <v>2.220558059873863</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.539011616934403</v>
+        <v>-5.635352266096835</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.597798202177743</v>
+        <v>0.5592619425127703</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.8927433081206557</v>
+        <v>-0.9886686889856484</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.278113288392859</v>
+        <v>2.220558059873863</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.528638240601317</v>
+        <v>-5.624978889763748</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.6083293097387825</v>
+        <v>0.5697930500738098</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.8823699317875684</v>
+        <v>-0.9782953126525611</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.290719071220516</v>
+        <v>2.23316384270152</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-5.40095393080702</v>
+        <v>-5.497294579969452</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.6642954070312261</v>
+        <v>0.6257591473662534</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.7546856219932719</v>
+        <v>-0.8506110028582646</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.372222030471819</v>
+        <v>2.314666801952823</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.46162052120941</v>
+        <v>-5.557961170371842</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.6267834433461426</v>
+        <v>0.5882471836811698</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.8363839387118056</v>
+        <v>-0.9323093195767983</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.30995771291657</v>
+        <v>2.252402484397575</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-5.396626661275764</v>
+        <v>-5.492967310438196</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.6568786899302292</v>
+        <v>0.6183424302652565</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.8095533241076502</v>
+        <v>-0.9054787049726429</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.330153784289692</v>
+        <v>2.272598555770697</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.497385297032762</v>
+        <v>-5.593725946195194</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.6207361752585081</v>
+        <v>0.5821999155935353</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.8983788928346557</v>
+        <v>-0.9943042736996484</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.281019382684567</v>
+        <v>2.223464154165572</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.453182459946862</v>
+        <v>-5.549523109109294</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.6442969126207054</v>
+        <v>0.6057606529557327</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.8541760557487552</v>
+        <v>-0.9501014366137479</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.313420687463944</v>
+        <v>2.255865458944949</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.490161487610305</v>
+        <v>-5.586502136772737</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.6279153020245758</v>
+        <v>0.589379042359603</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.8172021539574247</v>
+        <v>-0.9131275348224174</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.33401502900799</v>
+        <v>2.276459800488995</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.510219566475145</v>
+        <v>-5.606560215637577</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.6711398356616791</v>
+        <v>0.6326035759967064</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.8172021539574247</v>
+        <v>-0.9131275348224174</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.38526279419103</v>
+        <v>2.327707565672035</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-5.470288893297255</v>
+        <v>-5.566629542459687</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.6855528095270884</v>
+        <v>0.6470165498621157</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.7772714807795343</v>
+        <v>-0.873196861644527</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.407661902692017</v>
+        <v>2.350106674173022</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-5.42981854573455</v>
+        <v>-5.526159194896982</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.6966891767904402</v>
+        <v>0.6581529171254674</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.7368011332168294</v>
+        <v>-0.8327265140818221</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.42689233946791</v>
+        <v>2.369337110948915</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-5.364594364607345</v>
+        <v>-5.460935013769777</v>
       </c>
       <c r="E1988" t="n">
-        <v>0.7399662533340274</v>
+        <v>0.7014299936690547</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.6715769520896238</v>
+        <v>-0.7675023329546165</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.483214252236939</v>
+        <v>2.425659023717943</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-5.415088654964401</v>
+        <v>-5.511429304126833</v>
       </c>
       <c r="E1989" t="n">
-        <v>0.7157295094904854</v>
+        <v>0.6771932498255127</v>
       </c>
       <c r="F1989" t="n">
-        <v>-0.716597689215698</v>
+        <v>-0.8125230700806907</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.452162782260574</v>
+        <v>2.394607553741579</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749918</v>
+        <v>3.84519884274992</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-5.435200310999109</v>
+        <v>-5.531540960161541</v>
       </c>
       <c r="E1990" t="n">
-        <v>0.7089416394078425</v>
+        <v>0.6704053797428697</v>
       </c>
       <c r="F1990" t="n">
-        <v>-0.7055703442182788</v>
+        <v>-0.8014957250832715</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.460035981590266</v>
+        <v>2.402480753071271</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.562265146267067</v>
+        <v>3.562265146267069</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.807331855895701</v>
+        <v>2.717249022032572</v>
       </c>
       <c r="D1991" t="n">
-        <v>-5.435200310999109</v>
+        <v>-5.531540960161541</v>
       </c>
       <c r="E1991" t="n">
-        <v>0.7089416394078425</v>
+        <v>0.6704053797428697</v>
       </c>
       <c r="F1991" t="n">
-        <v>-0.7055703442182788</v>
+        <v>-0.8014957250832715</v>
       </c>
       <c r="G1991" t="n">
-        <v>2.800395652882069</v>
+        <v>2.71031281901894</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240610.xlsx
+++ b/tame_output/ON/bt/strategyON_20240610.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>61.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>53.3%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,27 +839,27 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-39.9%</t>
+          <t>-23.8%</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-78.5%</t>
+          <t>-78.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>449.9%</t>
+          <t>453.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-714.7%</t>
+          <t>-716.3%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-24.5%</t>
+          <t>-24.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-9.1%</t>
+          <t>-9.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-309.2%</t>
+          <t>-310.3%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-34.6%</t>
+          <t>-34.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-29.6%</t>
+          <t>-28.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-304.1%</t>
+          <t>-302.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,37 +1476,37 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.2%</t>
+          <t>-15.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-175.0%</t>
+          <t>-205.2%</t>
         </is>
       </c>
     </row>
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.304461982734203</v>
+        <v>-9.303069491845626</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.6065359524693927</v>
+        <v>-0.6059789561139621</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.875025807444799</v>
+        <v>-1.873633316556221</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.990589780471157</v>
+        <v>1.991425275004304</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.663992305238205</v>
+        <v>-9.662599814349628</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7449977781729431</v>
+        <v>-0.7444407818175125</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.875025807444799</v>
+        <v>-1.873633316556221</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.995940083769207</v>
+        <v>1.996775578302354</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.50317028234131</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.714341368692427</v>
+        <v>-9.71294887780385</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7572213835974546</v>
+        <v>-0.7566643872420236</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.925374870899021</v>
+        <v>-1.923982380010443</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.973646665653852</v>
+        <v>1.974482160186998</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.811960646113823</v>
+        <v>-9.810568155225246</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7932273439442441</v>
+        <v>-0.7926703475888135</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.022994148320417</v>
+        <v>-2.02160165743184</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.918116849822782</v>
+        <v>1.918952344355929</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937497</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.959486734119466</v>
+        <v>-9.958094243230889</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8493442228249291</v>
+        <v>-0.8487872264694984</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.170520236326061</v>
+        <v>-2.169127745437483</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.832494753340968</v>
+        <v>1.833330247874115</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.5027903991417</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.16374490944933</v>
+        <v>-10.16235241856075</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.925534295838232</v>
+        <v>-0.9249772994828014</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.29815918094005</v>
+        <v>-2.296766690051472</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.761424583691217</v>
+        <v>1.762260078224364</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.30555468365612</v>
+        <v>-10.30416219276754</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9777756510365117</v>
+        <v>-0.9772186546810802</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.469437978585626</v>
+        <v>-2.468045487697048</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.663139859588308</v>
+        <v>1.663975354121455</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.23208485198867</v>
+        <v>-10.23069236110009</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.9330160168761106</v>
+        <v>-0.93245902052068</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.395968146918177</v>
+        <v>-2.394575656029599</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.722593460082198</v>
+        <v>1.723428954615345</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.40720926937521</v>
+        <v>-10.40581677848663</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9885105630832109</v>
+        <v>-0.9879535667277803</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.571092564304721</v>
+        <v>-2.569700073416143</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.632074030397789</v>
+        <v>1.632909524930936</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.6416613633897</v>
+        <v>-10.64026887250112</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.089510565590603</v>
+        <v>-1.088953569235172</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.571092564304721</v>
+        <v>-2.569700073416143</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.624854865496193</v>
+        <v>1.62569036002934</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.92946520792694</v>
+        <v>-10.92807271703836</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.211304294179474</v>
+        <v>-1.210747297824044</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.858896408841959</v>
+        <v>-2.857503917953381</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.445500367999874</v>
+        <v>1.44633586253302</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.98225136352727</v>
+        <v>-10.98085887263869</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.231302966581049</v>
+        <v>-1.230745970225618</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.954571895424356</v>
+        <v>-2.953179404535778</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.389210865888992</v>
+        <v>1.390046360422138</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.10828815689556</v>
+        <v>-11.10689566600698</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.27902395529925</v>
+        <v>-1.278466958943819</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.929320272614614</v>
+        <v>-2.927927781726036</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.407055568203952</v>
+        <v>1.407891062737099</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.05627264292674</v>
+        <v>-11.05488015203817</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.254227414025324</v>
+        <v>-1.253670417669893</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.929320272614614</v>
+        <v>-2.927927781726036</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.411045903890353</v>
+        <v>1.411881398423499</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.600038265158922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.19794448465086</v>
+        <v>-11.19655199376229</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.312371377613713</v>
+        <v>-1.311814381258283</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.929320272614614</v>
+        <v>-2.927927781726036</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.409570676991611</v>
+        <v>1.410406171524758</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940719</v>
+        <v>3.69157173394072</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.14835364022603</v>
+        <v>-11.14696114933745</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.277481629678908</v>
+        <v>-1.276924633323477</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.87972942818978</v>
+        <v>-2.878336937301202</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.454378593811384</v>
+        <v>1.45521408834453</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.67684154977058</v>
+        <v>3.676841549770581</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.13554624722125</v>
+        <v>-11.13415375633268</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.285409806123681</v>
+        <v>-1.28485280976825</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.928585203198681</v>
+        <v>-2.927192712310103</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.41201399515936</v>
+        <v>1.412849489692507</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615284</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.90970109450184</v>
+        <v>-10.90830860361327</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.185492671999709</v>
+        <v>-1.184935675644277</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.886658527611517</v>
+        <v>-2.885266036722939</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.446749073547867</v>
+        <v>1.447584568081014</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812103</v>
+        <v>3.684843823812104</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.78512243816425</v>
+        <v>-10.78372994727568</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.134522064908613</v>
+        <v>-1.133965068553182</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.886658527611517</v>
+        <v>-2.885266036722939</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.447888218103926</v>
+        <v>1.448723712637073</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646217</v>
+        <v>3.710935533646218</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.83801772620854</v>
+        <v>-10.83662523531996</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.153046405964219</v>
+        <v>-1.152489409608789</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.881703181523071</v>
+        <v>-2.880310690634493</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.453495199919101</v>
+        <v>1.454330694452248</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611568</v>
+        <v>3.76895167461157</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.76588455092066</v>
+        <v>-10.76449206003208</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.118459431610431</v>
+        <v>-1.117902435255</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.881703181523071</v>
+        <v>-2.880310690634493</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.459228904157738</v>
+        <v>1.460064398690885</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.69451815831101</v>
+        <v>-10.69312566742243</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.099650136960437</v>
+        <v>-1.099093140605007</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.810336788913423</v>
+        <v>-2.808944298024845</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.492311477329662</v>
+        <v>1.493146971862808</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74770266023241</v>
+        <v>3.747702660232412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.43068129110694</v>
+        <v>-10.42928880021836</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.003998871391717</v>
+        <v>-1.003441875036286</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.810336788913423</v>
+        <v>-2.808944298024845</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.482427996016754</v>
+        <v>1.4832634905499</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436226</v>
+        <v>3.766317079436228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.16343949023854</v>
+        <v>-10.16204699934997</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.898936711543731</v>
+        <v>-0.8983797151883004</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.810336788913423</v>
+        <v>-2.808944298024845</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.48059343551738</v>
+        <v>1.481428930050527</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311946</v>
+        <v>3.784684521311948</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.06553245156205</v>
+        <v>-10.06413996067348</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8600742110465958</v>
+        <v>-0.8595172146911652</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.742351039052866</v>
+        <v>-2.740958548164288</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.521084570460253</v>
+        <v>1.5219200649934</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097243</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.04157891058609</v>
+        <v>-10.04018641969752</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8498242885107188</v>
+        <v>-0.8492672921552882</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.718397498076909</v>
+        <v>-2.717005007188331</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.536125201191321</v>
+        <v>1.536960695724468</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017771</v>
+        <v>3.789311112017772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.777518972263298</v>
+        <v>-9.776126481374721</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7574606293433526</v>
+        <v>-0.756903632987922</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.454337559754113</v>
+        <v>-2.452945068865535</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.681300848023247</v>
+        <v>1.682136342556394</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839724</v>
+        <v>3.833252747839726</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.070439348758461</v>
+        <v>-9.069046857869884</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.4774158136017186</v>
+        <v>-0.4768588172462875</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.454337559754113</v>
+        <v>-2.452945068865535</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.678513814362946</v>
+        <v>1.679349308896093</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388726</v>
+        <v>3.839374447388728</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.03025505039227</v>
+        <v>-9.028862559503693</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.460998470367401</v>
+        <v>-0.46044147401197</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.414153261387922</v>
+        <v>-2.412760770499344</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.702968017270502</v>
+        <v>1.703803511803649</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.856161751626474</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.950185254854466</v>
+        <v>-8.948792763965889</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.4296037309315222</v>
+        <v>-0.4290467345760915</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.334083465850118</v>
+        <v>-2.33269097496154</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.750376715813941</v>
+        <v>1.751212210347088</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78733042929181</v>
+        <v>3.787330429291813</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.716704032624868</v>
+        <v>-8.715311541736291</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.3282868132018306</v>
+        <v>-0.3277298168464</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.100602243620519</v>
+        <v>-2.099209752731941</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.898389877989553</v>
+        <v>1.899225372522699</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785787</v>
+        <v>3.80163712278579</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.567037641617354</v>
+        <v>-8.565645150728777</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.2713124671117844</v>
+        <v>-0.2707554707563533</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.007698752377983</v>
+        <v>-2.006306261489406</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.951239762422115</v>
+        <v>1.952075256955262</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390427</v>
+        <v>3.76318224839043</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.434762167986467</v>
+        <v>-8.43336967709789</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.2230347909124024</v>
+        <v>-0.2224777945569714</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.875423278747097</v>
+        <v>-1.874030787858519</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.025972533347674</v>
+        <v>2.026808027880821</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105951</v>
+        <v>3.784718794105954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.244162493313313</v>
+        <v>-8.242770002424736</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.143979860355504</v>
+        <v>-0.1434228640000734</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.684823604073944</v>
+        <v>-1.683431113185366</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.143147398839202</v>
+        <v>2.143982893372349</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960986</v>
+        <v>3.753882571960989</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.995162694629732</v>
+        <v>-7.993770203741155</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.03147359965841323</v>
+        <v>-0.03091660330298218</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.684823604073944</v>
+        <v>-1.683431113185366</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.156053740062861</v>
+        <v>2.156889234596008</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607647</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.100752684402837</v>
+        <v>-8.09936019351426</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2016855251668734</v>
+        <v>-0.2011285288114428</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.790413593847048</v>
+        <v>-1.78902110295847</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.96472381659978</v>
+        <v>1.965559311132926</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987905</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.119487586521434</v>
+        <v>-8.118095095632857</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1606351441372258</v>
+        <v>-0.1600781477817952</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.79600960350718</v>
+        <v>-1.794617112618602</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.009910552680787</v>
+        <v>2.010746047213934</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033368671081</v>
+        <v>3.760333686710814</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.971547545113834</v>
+        <v>-7.970155054225257</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.2213380502623536</v>
+        <v>-0.220781053906923</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.775688687598622</v>
+        <v>-1.774296196710044</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.902224179537755</v>
+        <v>1.903059674070901</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409208</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.95438939498254</v>
+        <v>-7.952996904093963</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.2231887764633145</v>
+        <v>-0.2226317801078834</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.758530537467328</v>
+        <v>-1.75713804657875</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.903805083363053</v>
+        <v>1.9046405778962</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.729969716098112</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.91084098821185</v>
+        <v>-7.909448497323273</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.2127300258501315</v>
+        <v>-0.2121730294947004</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.758530537467328</v>
+        <v>-1.75713804657875</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.89684447126796</v>
+        <v>1.897679965801107</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493419</v>
+        <v>3.782922533493423</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.668692594757991</v>
+        <v>-7.667300103869414</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1014083140874451</v>
+        <v>-0.1008513177320141</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.758530537467328</v>
+        <v>-1.75713804657875</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.911306825649103</v>
+        <v>1.91214232018225</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722816</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.56043345763547</v>
+        <v>-7.559040966746893</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.06357253877924141</v>
+        <v>-0.06301554242381036</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.758530537467328</v>
+        <v>-1.75713804657875</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.905838946108298</v>
+        <v>1.906674440641445</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792049</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.437142322818339</v>
+        <v>-7.435749831929762</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.01675799084181184</v>
+        <v>-0.01620099448638124</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.635239402650197</v>
+        <v>-1.633846911761619</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.977311721009153</v>
+        <v>1.978147215542299</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.81245367891991</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.415993123914896</v>
+        <v>-7.414600633026319</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.0005973330431094936</v>
+        <v>-4.033668767888798e-05</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.614090203746754</v>
+        <v>-1.612697712858176</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.997702218588544</v>
+        <v>1.998537713121691</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318092</v>
+        <v>3.748328408318096</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.172227681931451</v>
+        <v>-7.170835191042874</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.09268955209731899</v>
+        <v>0.0932465484527496</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.614090203746754</v>
+        <v>-1.612697712858176</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.993482926935595</v>
+        <v>1.994318421468741</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057529</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.070464861654156</v>
+        <v>-7.069072370765579</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1355189941282529</v>
+        <v>0.1360759904836835</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.600871135354325</v>
+        <v>-1.599478644465747</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.003538681891068</v>
+        <v>2.004374176424215</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279185</v>
+        <v>3.826354974279188</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.820614467705082</v>
+        <v>-6.819221976816505</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2282012266915849</v>
+        <v>0.2287582230470155</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.600871135354325</v>
+        <v>-1.599478644465747</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.99628075687477</v>
+        <v>1.997116251407917</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011498</v>
+        <v>3.835957987011501</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.644722375237649</v>
+        <v>-6.643329884349072</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3021571871992066</v>
+        <v>0.3027141835546376</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.600871135354325</v>
+        <v>-1.599478644465747</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.999879880395419</v>
+        <v>2.000715374928566</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392991</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.473275912215185</v>
+        <v>-6.471883421326608</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.384063278462746</v>
+        <v>0.3846202748181766</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.429424672331862</v>
+        <v>-1.428032181443284</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.116075264263451</v>
+        <v>2.116910758796597</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.773765222632785</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.248242912546362</v>
+        <v>-6.246850421657785</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4730969559465721</v>
+        <v>0.4736539523020027</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.204391672663039</v>
+        <v>-1.202999181774461</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.250115541681041</v>
+        <v>2.250951036214188</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883077</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.184607170312428</v>
+        <v>-6.183214679423851</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.503246053894463</v>
+        <v>0.503803050249894</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.140755930429105</v>
+        <v>-1.139363439540527</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.292991788075719</v>
+        <v>2.293827282608866</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074782</v>
+        <v>3.798814771074785</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.140844989006586</v>
+        <v>-6.139452498118009</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5019451852005954</v>
+        <v>0.502502181556026</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.140755930429105</v>
+        <v>-1.139363439540527</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.274186046859515</v>
+        <v>2.275021541392662</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242296</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.900414492201726</v>
+        <v>-5.899022001313149</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5998604605474167</v>
+        <v>0.6004174569028478</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.9003254336242443</v>
+        <v>-0.8989329427356665</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.420187421567308</v>
+        <v>2.421022916100455</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367684</v>
+        <v>3.821593509367688</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.828171924030531</v>
+        <v>-5.826779433141954</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6326868016507148</v>
+        <v>0.6332437980061458</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.9003254336242443</v>
+        <v>-0.8989329427356665</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.424116735402129</v>
+        <v>2.424952229935275</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879966</v>
+        <v>3.822326997879969</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.775173601749144</v>
+        <v>-5.773781110860567</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6545647144806099</v>
+        <v>0.655121710836041</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.8449891746223055</v>
+        <v>-0.8435966837337276</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.457997074720632</v>
+        <v>2.458832569253778</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502339</v>
+        <v>3.848616626502342</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.666368716269417</v>
+        <v>-5.66497622538084</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.6950847398924944</v>
+        <v>0.695641736247925</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.8449891746223055</v>
+        <v>-0.8435966837337276</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.454995145940625</v>
+        <v>2.455830640473772</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675938</v>
+        <v>3.818668951675941</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.562786607879484</v>
+        <v>-5.561394116990907</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.7380966202590815</v>
+        <v>0.7386536166145126</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.8474496195133334</v>
+        <v>-0.8460571286247556</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.455097916016623</v>
+        <v>2.45593341054977</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327452753995</v>
+        <v>3.843274527539954</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.429918918816206</v>
+        <v>-5.428526427927629</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.8071378786862162</v>
+        <v>0.8076948750416468</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.8474496195133334</v>
+        <v>-0.8460571286247556</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.470992098818446</v>
+        <v>2.471827593351593</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496262</v>
+        <v>3.845047386496266</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.270403815296836</v>
+        <v>-5.269011324408259</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.872089764534266</v>
+        <v>0.8726467608896966</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.6879345159939635</v>
+        <v>-0.6865420251053856</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.56784700537037</v>
+        <v>2.568682499903517</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551577003</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-5.125731670197099</v>
+        <v>-5.124339179308522</v>
       </c>
       <c r="E1932" t="n">
-        <v>0.9400467251356006</v>
+        <v>0.9406037214910317</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.5432623708942261</v>
+        <v>-0.5418698800056483</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.664738394991652</v>
+        <v>2.665573889524799</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942108</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-5.185606497554791</v>
+        <v>-5.184214006666214</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9021342855939496</v>
+        <v>0.9026912819493802</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.6031371982519182</v>
+        <v>-0.6017447073633404</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.614850989978463</v>
+        <v>2.61568648451161</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.76264747767452</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-5.098806999775782</v>
+        <v>-5.097414508887205</v>
       </c>
       <c r="E1934" t="n">
-        <v>0.9592545780281192</v>
+        <v>0.9598115743835502</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.6031371982519182</v>
+        <v>-0.6017447073633404</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.637251483301029</v>
+        <v>2.638086977834176</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430694</v>
+        <v>3.729146398430699</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-5.101276706237588</v>
+        <v>-5.099884215349011</v>
       </c>
       <c r="E1935" t="n">
-        <v>0.9583390968168093</v>
+        <v>0.9588960931722399</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.6056069047137245</v>
+        <v>-0.6042144138251466</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.635842060797357</v>
+        <v>2.636677555330504</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003602</v>
+        <v>3.743220196003607</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-5.169646892561598</v>
+        <v>-5.168254401673021</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.9419979447619071</v>
+        <v>0.9425549411173377</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.5963312056775095</v>
+        <v>-0.5949387147889317</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.652414402693788</v>
+        <v>2.653249897226935</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.71417913950837</v>
+        <v>3.714179139508375</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.278185073477732</v>
+        <v>-5.276792582589155</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.8890193810273446</v>
+        <v>0.8895763773827756</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.5963312056775095</v>
+        <v>-0.5949387147889317</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.64285111132568</v>
+        <v>2.643686605858826</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417703</v>
+        <v>3.710906731417708</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.309178232806437</v>
+        <v>-5.30778574191786</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.7013316823362494</v>
+        <v>0.70188867869168</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.5963312056775095</v>
+        <v>-0.5949387147889317</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.467560676366066</v>
+        <v>2.468396170899213</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.746042526205905</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-5.133703973013969</v>
+        <v>-5.132311482125392</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.7760886182450246</v>
+        <v>0.7766456146004557</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.5963312056775095</v>
+        <v>-0.5949387147889317</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.472127908357854</v>
+        <v>2.472963402891001</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225444</v>
+        <v>3.765024323225449</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-5.244640225655218</v>
+        <v>-5.243247734766641</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.7074561459497324</v>
+        <v>0.708013142305163</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.5963312056775095</v>
+        <v>-0.5949387147889317</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.447869937119061</v>
+        <v>2.448705431652208</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111299</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.447666803198451</v>
+        <v>-5.446274312309874</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.6293769001523444</v>
+        <v>0.6299338965077754</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.7993577832207429</v>
+        <v>-0.7979652923321651</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.329185375813027</v>
+        <v>2.330020870346174</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264163</v>
+        <v>3.784343952264168</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-5.289741204263158</v>
+        <v>-5.288348713374581</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.7027195261585941</v>
+        <v>0.7032765225140247</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.7993577832207429</v>
+        <v>-0.7979652923321651</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.339357762245159</v>
+        <v>2.340193256778306</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742304</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-5.20349774123678</v>
+        <v>-5.202105250348203</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.7321631819430054</v>
+        <v>0.7327201782984361</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.7993577832207429</v>
+        <v>-0.7979652923321651</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.334304032819019</v>
+        <v>2.335139527352166</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316047</v>
+        <v>3.752027499316052</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.24880456063576</v>
+        <v>-5.247412069747183</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.7058162296279389</v>
+        <v>0.7063732259833699</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.8401679462299737</v>
+        <v>-0.8387754553413959</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.301593710458007</v>
+        <v>2.302429204991153</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803196</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-5.277837665338061</v>
+        <v>-5.276445174449484</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.6947548607801202</v>
+        <v>0.6953118571355508</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.8401679462299737</v>
+        <v>-0.8387754553413959</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.302145583491108</v>
+        <v>2.302981078024255</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809498</v>
+        <v>3.733390600809503</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-5.185027183887201</v>
+        <v>-5.183634692998624</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.6611517452518298</v>
+        <v>0.6617087416072605</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.7473574647791144</v>
+        <v>-0.7459649738905365</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.287104564252989</v>
+        <v>2.287940058786136</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.74828581656043</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-5.229416653216629</v>
+        <v>-5.228024162328052</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.6452694334446596</v>
+        <v>0.6458264298000902</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.791746934108542</v>
+        <v>-0.7903544432199642</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.262344358579933</v>
+        <v>2.26317985311308</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472738</v>
+        <v>3.721077195472742</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-5.116745434980379</v>
+        <v>-5.115352944091802</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.6854136292508826</v>
+        <v>0.6859706256063132</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.6790757158722918</v>
+        <v>-0.6776832249837139</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.325022798033407</v>
+        <v>2.325858292566553</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798542</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-5.004368433797706</v>
+        <v>-5.002975942909129</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.735855725554619</v>
+        <v>0.7364127219100498</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.6790757158722918</v>
+        <v>-0.6776832249837139</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.330514093864074</v>
+        <v>2.331349588397221</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498869</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-5.202603002684437</v>
+        <v>-5.20121051179586</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.6680590997684659</v>
+        <v>0.6686160961238965</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.8773102847590224</v>
+        <v>-0.8759177938704445</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.223070554300575</v>
+        <v>2.223906048833721</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705325</v>
+        <v>3.64306962170533</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-5.285604283709715</v>
+        <v>-5.284211792821139</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.4732143073590076</v>
+        <v>0.4737713037144382</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.8958811692861961</v>
+        <v>-0.8944886783976183</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.050283743584924</v>
+        <v>2.051119238118071</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.68271631072927</v>
+        <v>3.682716310729274</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.394218362153047</v>
+        <v>-5.39282587126447</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.5499183367008804</v>
+        <v>0.5504753330563115</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.8958811692861961</v>
+        <v>-0.8944886783976183</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.170433404304129</v>
+        <v>2.171268898837276</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190769</v>
+        <v>3.733012441190773</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.48081694513415</v>
+        <v>-5.479424454245573</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.5297919296107625</v>
+        <v>0.5303489259661931</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.8958811692861961</v>
+        <v>-0.8944886783976183</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.184946430406452</v>
+        <v>2.185781924939599</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913429</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.442433282575998</v>
+        <v>-5.441040791687421</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.5425648359763917</v>
+        <v>0.5431218323318223</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.8574975067280449</v>
+        <v>-0.8561050158394671</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.205396069283712</v>
+        <v>2.206231563816858</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532485</v>
+        <v>3.751147197532489</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-5.265316952540832</v>
+        <v>-5.263924461652255</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.6101403968357597</v>
+        <v>0.6106973931911908</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.8574975067280449</v>
+        <v>-0.8561050158394671</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.202125098129013</v>
+        <v>2.20296059266216</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.741328448793906</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-5.310409197374378</v>
+        <v>-5.309016706485801</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.5927868906642546</v>
+        <v>0.5933438870196857</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.9193935498974347</v>
+        <v>-0.9180010590088569</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.165670863989293</v>
+        <v>2.166506358522439</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011236</v>
+        <v>3.75072937701124</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-5.13103377613561</v>
+        <v>-5.129641285247033</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.658324034466176</v>
+        <v>0.6588810308216071</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.762616791726716</v>
+        <v>-0.7612243008381382</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.253523894198138</v>
+        <v>2.254359388731285</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982231</v>
+        <v>3.716991718982235</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-5.176047989656217</v>
+        <v>-5.17465549876764</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.6211258043895231</v>
+        <v>0.6216828007449542</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.7929656870413206</v>
+        <v>-0.7915731961527428</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.216122012340966</v>
+        <v>2.216957506874112</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509538</v>
+        <v>3.737026608509541</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.443052499928652</v>
+        <v>-5.441660009040075</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.5200155626194949</v>
+        <v>0.5205725589749259</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.9873287250842693</v>
+        <v>-0.9859362341956914</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.105195751854142</v>
+        <v>2.106031246387289</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.702309454760815</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.544250281365825</v>
+        <v>-5.542857790477248</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.4787403719411274</v>
+        <v>0.479297368296558</v>
       </c>
       <c r="F1960" t="n">
-        <v>-1.055737538629588</v>
+        <v>-1.054345047741011</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.063354385623452</v>
+        <v>2.064189880156599</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815461</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.511774695195053</v>
+        <v>-5.510382204306476</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.4893305679637527</v>
+        <v>0.4898875643191838</v>
       </c>
       <c r="F1961" t="n">
-        <v>-1.055737538629588</v>
+        <v>-1.054345047741011</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.060954347177768</v>
+        <v>2.061789841710915</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.709510443378106</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.492736567487755</v>
+        <v>-5.491344076599178</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.4934705382549169</v>
+        <v>0.4940275346103475</v>
       </c>
       <c r="F1962" t="n">
-        <v>-1.113921149960783</v>
+        <v>-1.112528659072205</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.022568899587297</v>
+        <v>2.023404394120444</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131252</v>
+        <v>3.731064473131256</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.523863198638374</v>
+        <v>-5.522470707749797</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.65860175473335</v>
+        <v>0.6591587510887806</v>
       </c>
       <c r="F1963" t="n">
-        <v>-1.113921149960783</v>
+        <v>-1.112528659072205</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.200150768525977</v>
+        <v>2.200986263059124</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067868</v>
+        <v>3.722447362067872</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.576183579239165</v>
+        <v>-5.574791088350588</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.6385069314791667</v>
+        <v>0.6390639278345978</v>
       </c>
       <c r="F1964" t="n">
-        <v>-1.078974289951911</v>
+        <v>-1.077581799063333</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.221952213517434</v>
+        <v>2.222787708050581</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789125</v>
+        <v>3.787425580789129</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.596440877768123</v>
+        <v>-5.595048386879546</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.6364125424645097</v>
+        <v>0.6369695388199403</v>
       </c>
       <c r="F1965" t="n">
-        <v>-1.078974289951911</v>
+        <v>-1.077581799063333</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.22796074391436</v>
+        <v>2.228796238447507</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.78150125051991</v>
+        <v>3.781501250519914</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.448697907533121</v>
+        <v>-5.447305416644544</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.7746623783505324</v>
+        <v>0.7752193747059635</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.9111669327170276</v>
+        <v>-0.9097744418284498</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.407797806047312</v>
+        <v>2.408633300580459</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181173</v>
+        <v>3.802245929181177</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.550712590064342</v>
+        <v>-5.549320099175765</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.7366501268695251</v>
+        <v>0.7372071232249557</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.9111669327170276</v>
+        <v>-0.9097744418284498</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.410591427578793</v>
+        <v>2.41142692211194</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.805608985394735</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.544559884011558</v>
+        <v>-5.543167393122981</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.7397735576822972</v>
+        <v>0.7403305540377279</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.9050142266642434</v>
+        <v>-0.9036217357756655</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.414945399602122</v>
+        <v>2.415780894135269</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890617</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.687325216834208</v>
+        <v>-5.685932725945631</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.6817479012933472</v>
+        <v>0.6823048976487782</v>
       </c>
       <c r="F1969" t="n">
-        <v>-1.047779559486894</v>
+        <v>-1.046387068598316</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.328366676648642</v>
+        <v>2.329202171181789</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798428</v>
+        <v>3.867362636798432</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.625027218058086</v>
+        <v>-5.623634727169509</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.7730026546006172</v>
+        <v>0.7735596509560478</v>
       </c>
       <c r="F1970" t="n">
-        <v>-1.047779559486894</v>
+        <v>-1.046387068598316</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.394702230445463</v>
+        <v>2.39553772497861</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992193</v>
+        <v>3.848729139992196</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-5.423237020392928</v>
+        <v>-5.421844529504351</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.5622996060560781</v>
+        <v>0.5628566024115091</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.8497613673177393</v>
+        <v>-0.8483688764291615</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.222094018136354</v>
+        <v>2.2229295126695</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852428</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-5.363346338750334</v>
+        <v>-5.361953847861757</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.6565461110352908</v>
+        <v>0.6571031073907214</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.7898706856751458</v>
+        <v>-0.788478194786568</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.328318659444085</v>
+        <v>2.329154153977231</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319547</v>
+        <v>3.81906330031955</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.461086883375309</v>
+        <v>-5.459694392486732</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.6320776293013446</v>
+        <v>0.6326346256567756</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.8057599638081261</v>
+        <v>-0.8043674729195482</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.33341282868034</v>
+        <v>2.334248323213487</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489388</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.637424643498238</v>
+        <v>-5.636032152609661</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.5600785060768447</v>
+        <v>0.5606355024322753</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.9820977239310555</v>
+        <v>-0.9807052330424777</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.226146153431254</v>
+        <v>2.226981647964401</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397798</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.636735271337015</v>
+        <v>-5.635342780448438</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.5588458729812626</v>
+        <v>0.5594028693366933</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.9820977239310555</v>
+        <v>-0.9807052330424777</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.224637771471183</v>
+        <v>2.22547326600433</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024963</v>
+        <v>3.836023391024966</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.643306236391608</v>
+        <v>-5.641913745503031</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.5560803543948616</v>
+        <v>0.5566373507502922</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.9886686889856484</v>
+        <v>-0.9872761980970706</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.220558059873863</v>
+        <v>2.22139355440701</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863226</v>
+        <v>3.821591150863229</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.635352266096835</v>
+        <v>-5.633959775208258</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.5592619425127703</v>
+        <v>0.5598189388682013</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.9886686889856484</v>
+        <v>-0.9872761980970706</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.220558059873863</v>
+        <v>2.22139355440701</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947585</v>
+        <v>3.833040181947588</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.624978889763748</v>
+        <v>-5.623586398875172</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.5697930500738098</v>
+        <v>0.5703500464292408</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.9782953126525611</v>
+        <v>-0.9769028217639832</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.23316384270152</v>
+        <v>2.233999337234667</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326877</v>
+        <v>3.822707244326881</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-5.497294579969452</v>
+        <v>-5.495902089080875</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.6257591473662534</v>
+        <v>0.626316143721684</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.8506110028582646</v>
+        <v>-0.8492185119696868</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.314666801952823</v>
+        <v>2.31550229648597</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314553</v>
+        <v>3.828837911314556</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.557961170371842</v>
+        <v>-5.556568679483265</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.5882471836811698</v>
+        <v>0.5888041800366004</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.9323093195767983</v>
+        <v>-0.9309168286882205</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.252402484397575</v>
+        <v>2.253237978930722</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690028</v>
+        <v>3.816866067690031</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-5.492967310438196</v>
+        <v>-5.491574819549619</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.6183424302652565</v>
+        <v>0.6188994266206871</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.9054787049726429</v>
+        <v>-0.9040862140840651</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.272598555770697</v>
+        <v>2.273434050303844</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674311</v>
+        <v>3.817961388674314</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.593725946195194</v>
+        <v>-5.592333455306617</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.5821999155935353</v>
+        <v>0.5827569119489659</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.9943042736996484</v>
+        <v>-0.9929117828110705</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.223464154165572</v>
+        <v>2.224299648698718</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.82671377916322</v>
+        <v>3.826713779163224</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.549523109109294</v>
+        <v>-5.548130618220717</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.6057606529557327</v>
+        <v>0.6063176493111633</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.9501014366137479</v>
+        <v>-0.9487089457251701</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.255865458944949</v>
+        <v>2.256700953478096</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022905</v>
+        <v>3.838228663022909</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.586502136772737</v>
+        <v>-5.58510964588416</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.589379042359603</v>
+        <v>0.5899360387150336</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.9131275348224174</v>
+        <v>-0.9117350439338395</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.276459800488995</v>
+        <v>2.277295295022141</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042139</v>
+        <v>3.863924114042143</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.606560215637577</v>
+        <v>-5.605167724749</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.6326035759967064</v>
+        <v>0.633160572352137</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.9131275348224174</v>
+        <v>-0.9117350439338395</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.327707565672035</v>
+        <v>2.328543060205181</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86536771507828</v>
+        <v>3.865367715078284</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-5.566629542459687</v>
+        <v>-5.56523705157111</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.6470165498621157</v>
+        <v>0.6475735462175463</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.873196861644527</v>
+        <v>-0.8718043707559492</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.350106674173022</v>
+        <v>2.350942168706168</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232396</v>
+        <v>3.8645188762324</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-5.526159194896982</v>
+        <v>-5.524766704008405</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.6581529171254674</v>
+        <v>0.6587099134808985</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.8327265140818221</v>
+        <v>-0.8313340231932442</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.369337110948915</v>
+        <v>2.370172605482062</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162111</v>
+        <v>3.842576394162115</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-5.460935013769777</v>
+        <v>-5.4595425228812</v>
       </c>
       <c r="E1988" t="n">
-        <v>0.7014299936690547</v>
+        <v>0.7019869900244853</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.7675023329546165</v>
+        <v>-0.7661098420660386</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.425659023717943</v>
+        <v>2.42649451825109</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639817</v>
+        <v>3.84009022063982</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-5.511429304126833</v>
+        <v>-5.510036813238256</v>
       </c>
       <c r="E1989" t="n">
-        <v>0.6771932498255127</v>
+        <v>0.6777502461809433</v>
       </c>
       <c r="F1989" t="n">
-        <v>-0.8125230700806907</v>
+        <v>-0.8111305791921128</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.394607553741579</v>
+        <v>2.395443048274726</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84519884274992</v>
+        <v>3.845198842749923</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-5.531540960161541</v>
+        <v>-5.530148469272964</v>
       </c>
       <c r="E1990" t="n">
-        <v>0.6704053797428697</v>
+        <v>0.6709623760983003</v>
       </c>
       <c r="F1990" t="n">
-        <v>-0.8014957250832715</v>
+        <v>-0.8001032341946936</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.402480753071271</v>
+        <v>2.403316247604418</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.562265146267069</v>
+        <v>3.813580557712028</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.717249022032572</v>
+        <v>2.878744993712149</v>
       </c>
       <c r="D1991" t="n">
-        <v>-5.531540960161541</v>
+        <v>-5.547461440927848</v>
       </c>
       <c r="E1991" t="n">
-        <v>0.6704053797428697</v>
+        <v>0.6594039930272624</v>
       </c>
       <c r="F1991" t="n">
-        <v>-0.8014957250832715</v>
+        <v>-0.7847417403392911</v>
       </c>
       <c r="G1991" t="n">
-        <v>2.71031281901894</v>
+        <v>2.407899949508574</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240610.xlsx
+++ b/tame_output/ON/bt/strategyON_20240610.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>59.1%</t>
         </is>
       </c>
     </row>
@@ -758,12 +758,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-21.1%</t>
+          <t>-20.9%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-23.8%</t>
+          <t>-22.1%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-81.5%</t>
+          <t>-81.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.9%</t>
+          <t>108.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>86.2%</t>
+          <t>86.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,22 +982,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-9.4%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.9%</t>
+          <t>-51.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-78.3%</t>
+          <t>-77.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.0%</t>
+          <t>453.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.4%</t>
+          <t>-10.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-716.3%</t>
+          <t>-704.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,22 +1140,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-39.1%</t>
+          <t>-37.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-24.4%</t>
+          <t>-25.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-9.3%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-310.3%</t>
+          <t>-303.7%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-34.4%</t>
+          <t>-32.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.6%</t>
+          <t>-31.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-28.8%</t>
+          <t>-26.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-156.7%</t>
+          <t>-155.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-302.5%</t>
+          <t>-289.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.8%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-29.7%</t>
+          <t>-27.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.0%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-205.2%</t>
+          <t>-195.8%</t>
         </is>
       </c>
     </row>
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317613</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.303069491845626</v>
+        <v>-9.304461982734203</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.6059789561139621</v>
+        <v>-0.6065359524693927</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.873633316556221</v>
+        <v>-1.875025807444799</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.991425275004304</v>
+        <v>1.990589780471157</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.662599814349628</v>
+        <v>-9.663992305238205</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7444407818175125</v>
+        <v>-0.7449977781729431</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.873633316556221</v>
+        <v>-1.875025807444799</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.996775578302354</v>
+        <v>1.995940083769207</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.71294887780385</v>
+        <v>-9.714341368692427</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7566643872420236</v>
+        <v>-0.7572213835974546</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.923982380010443</v>
+        <v>-1.925374870899021</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.974482160186998</v>
+        <v>1.973646665653852</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.810568155225246</v>
+        <v>-9.811960646113823</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7926703475888135</v>
+        <v>-0.7932273439442441</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.02160165743184</v>
+        <v>-2.022994148320417</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.918952344355929</v>
+        <v>1.918116849822782</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.958094243230889</v>
+        <v>-9.959486734119466</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8487872264694984</v>
+        <v>-0.8493442228249291</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.169127745437483</v>
+        <v>-2.170520236326061</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.833330247874115</v>
+        <v>1.832494753340968</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.16235241856075</v>
+        <v>-10.16374490944933</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.9249772994828014</v>
+        <v>-0.925534295838232</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.296766690051472</v>
+        <v>-2.29815918094005</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.762260078224364</v>
+        <v>1.761424583691217</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.30416219276754</v>
+        <v>-10.30555468365612</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9772186546810802</v>
+        <v>-0.9777756510365117</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.468045487697048</v>
+        <v>-2.469437978585626</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.663975354121455</v>
+        <v>1.663139859588308</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.23069236110009</v>
+        <v>-10.23208485198867</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.93245902052068</v>
+        <v>-0.9330160168761106</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.394575656029599</v>
+        <v>-2.395968146918177</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.723428954615345</v>
+        <v>1.722593460082198</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.40581677848663</v>
+        <v>-10.40720926937521</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9879535667277803</v>
+        <v>-0.9885105630832109</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.569700073416143</v>
+        <v>-2.571092564304721</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.632909524930936</v>
+        <v>1.632074030397789</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.64026887250112</v>
+        <v>-10.6416613633897</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.088953569235172</v>
+        <v>-1.089510565590603</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.569700073416143</v>
+        <v>-2.571092564304721</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.62569036002934</v>
+        <v>1.624854865496193</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.92807271703836</v>
+        <v>-10.92946520792694</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.210747297824044</v>
+        <v>-1.211304294179474</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.857503917953381</v>
+        <v>-2.858896408841959</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.44633586253302</v>
+        <v>1.445500367999874</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.98085887263869</v>
+        <v>-10.98225136352727</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.230745970225618</v>
+        <v>-1.231302966581049</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.953179404535778</v>
+        <v>-2.954571895424356</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.390046360422138</v>
+        <v>1.389210865888992</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.10689566600698</v>
+        <v>-11.10828815689556</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.278466958943819</v>
+        <v>-1.27902395529925</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.927927781726036</v>
+        <v>-2.929320272614614</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.407891062737099</v>
+        <v>1.407055568203952</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.05488015203817</v>
+        <v>-11.05627264292674</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.253670417669893</v>
+        <v>-1.254227414025324</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.927927781726036</v>
+        <v>-2.929320272614614</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.411881398423499</v>
+        <v>1.411045903890353</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.19655199376229</v>
+        <v>-11.19794448465086</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.311814381258283</v>
+        <v>-1.312371377613713</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.927927781726036</v>
+        <v>-2.929320272614614</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.410406171524758</v>
+        <v>1.409570676991611</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.14696114933745</v>
+        <v>-11.14835364022603</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.276924633323477</v>
+        <v>-1.277481629678908</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.878336937301202</v>
+        <v>-2.87972942818978</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.45521408834453</v>
+        <v>1.454378593811384</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.13415375633268</v>
+        <v>-11.13554624722125</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.28485280976825</v>
+        <v>-1.285409806123681</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.927192712310103</v>
+        <v>-2.928585203198681</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.412849489692507</v>
+        <v>1.41201399515936</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.90830860361327</v>
+        <v>-10.90970109450184</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.184935675644277</v>
+        <v>-1.185492671999709</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.885266036722939</v>
+        <v>-2.886658527611517</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.447584568081014</v>
+        <v>1.446749073547867</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.78372994727568</v>
+        <v>-10.78512243816425</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.133965068553182</v>
+        <v>-1.134522064908613</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.885266036722939</v>
+        <v>-2.886658527611517</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.448723712637073</v>
+        <v>1.447888218103926</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.83662523531996</v>
+        <v>-10.83801772620854</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.152489409608789</v>
+        <v>-1.153046405964219</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.880310690634493</v>
+        <v>-2.881703181523071</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.454330694452248</v>
+        <v>1.453495199919101</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.76449206003208</v>
+        <v>-10.76588455092066</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.117902435255</v>
+        <v>-1.118459431610431</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.880310690634493</v>
+        <v>-2.881703181523071</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.460064398690885</v>
+        <v>1.459228904157738</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.69312566742243</v>
+        <v>-10.69451815831101</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.099093140605007</v>
+        <v>-1.099650136960437</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.808944298024845</v>
+        <v>-2.810336788913423</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.493146971862808</v>
+        <v>1.492311477329662</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.42928880021836</v>
+        <v>-10.43068129110694</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.003441875036286</v>
+        <v>-1.003998871391717</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.808944298024845</v>
+        <v>-2.810336788913423</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.4832634905499</v>
+        <v>1.482427996016754</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.16204699934997</v>
+        <v>-10.16343949023854</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.8983797151883004</v>
+        <v>-0.898936711543731</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.808944298024845</v>
+        <v>-2.810336788913423</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.481428930050527</v>
+        <v>1.48059343551738</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.06413996067348</v>
+        <v>-10.06553245156205</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8595172146911652</v>
+        <v>-0.8600742110465958</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.740958548164288</v>
+        <v>-2.742351039052866</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.5219200649934</v>
+        <v>1.521084570460253</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.04018641969752</v>
+        <v>-10.04157891058609</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8492672921552882</v>
+        <v>-0.8498242885107188</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.717005007188331</v>
+        <v>-2.718397498076909</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.536960695724468</v>
+        <v>1.536125201191321</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.776126481374721</v>
+        <v>-9.777518972263298</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.756903632987922</v>
+        <v>-0.7574606293433526</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.452945068865535</v>
+        <v>-2.454337559754113</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.682136342556394</v>
+        <v>1.681300848023247</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.069046857869884</v>
+        <v>-9.070439348758461</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.4768588172462875</v>
+        <v>-0.4774158136017186</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.452945068865535</v>
+        <v>-2.454337559754113</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.679349308896093</v>
+        <v>1.678513814362946</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.028862559503693</v>
+        <v>-9.03025505039227</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.46044147401197</v>
+        <v>-0.460998470367401</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.412760770499344</v>
+        <v>-2.414153261387922</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.703803511803649</v>
+        <v>1.702968017270502</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.948792763965889</v>
+        <v>-8.950185254854466</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.4290467345760915</v>
+        <v>-0.4296037309315222</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.33269097496154</v>
+        <v>-2.334083465850118</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.751212210347088</v>
+        <v>1.750376715813941</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.715311541736291</v>
+        <v>-8.716704032624868</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.3277298168464</v>
+        <v>-0.3282868132018306</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.099209752731941</v>
+        <v>-2.100602243620519</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.899225372522699</v>
+        <v>1.898389877989553</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.565645150728777</v>
+        <v>-8.567037641617354</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.2707554707563533</v>
+        <v>-0.2713124671117844</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.006306261489406</v>
+        <v>-2.007698752377983</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.952075256955262</v>
+        <v>1.951239762422115</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.43336967709789</v>
+        <v>-8.434762167986467</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.2224777945569714</v>
+        <v>-0.2230347909124024</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.874030787858519</v>
+        <v>-1.875423278747097</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.026808027880821</v>
+        <v>2.025972533347674</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.242770002424736</v>
+        <v>-8.244162493313313</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.1434228640000734</v>
+        <v>-0.143979860355504</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.683431113185366</v>
+        <v>-1.684823604073944</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.143982893372349</v>
+        <v>2.143147398839202</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.993770203741155</v>
+        <v>-7.995162694629732</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.03091660330298218</v>
+        <v>-0.03147359965841323</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.683431113185366</v>
+        <v>-1.684823604073944</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.156889234596008</v>
+        <v>2.156053740062861</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.09936019351426</v>
+        <v>-8.100752684402837</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2011285288114428</v>
+        <v>-0.2016855251668734</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.78902110295847</v>
+        <v>-1.790413593847048</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.965559311132926</v>
+        <v>1.96472381659978</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.118095095632857</v>
+        <v>-8.119487586521434</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1600781477817952</v>
+        <v>-0.1606351441372258</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.794617112618602</v>
+        <v>-1.79600960350718</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.010746047213934</v>
+        <v>2.009910552680787</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.970155054225257</v>
+        <v>-7.971547545113834</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.220781053906923</v>
+        <v>-0.2213380502623536</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.774296196710044</v>
+        <v>-1.775688687598622</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.903059674070901</v>
+        <v>1.902224179537755</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.952996904093963</v>
+        <v>-7.95438939498254</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.2226317801078834</v>
+        <v>-0.2231887764633145</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.75713804657875</v>
+        <v>-1.758530537467328</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.9046405778962</v>
+        <v>1.903805083363053</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.909448497323273</v>
+        <v>-7.91084098821185</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.2121730294947004</v>
+        <v>-0.2127300258501315</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.75713804657875</v>
+        <v>-1.758530537467328</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.897679965801107</v>
+        <v>1.89684447126796</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.667300103869414</v>
+        <v>-7.668692594757991</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1008513177320141</v>
+        <v>-0.1014083140874451</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.75713804657875</v>
+        <v>-1.758530537467328</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.91214232018225</v>
+        <v>1.911306825649103</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.559040966746893</v>
+        <v>-7.56043345763547</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.06301554242381036</v>
+        <v>-0.06357253877924141</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.75713804657875</v>
+        <v>-1.758530537467328</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.906674440641445</v>
+        <v>1.905838946108298</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.435749831929762</v>
+        <v>-7.437142322818339</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.01620099448638124</v>
+        <v>-0.01675799084181184</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.633846911761619</v>
+        <v>-1.635239402650197</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.978147215542299</v>
+        <v>1.977311721009153</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.414600633026319</v>
+        <v>-7.415993123914896</v>
       </c>
       <c r="E1916" t="n">
-        <v>-4.033668767888798e-05</v>
+        <v>-0.0005973330431094936</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.612697712858176</v>
+        <v>-1.614090203746754</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.998537713121691</v>
+        <v>1.997702218588544</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.170835191042874</v>
+        <v>-7.172227681931451</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.0932465484527496</v>
+        <v>0.09268955209731899</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.612697712858176</v>
+        <v>-1.614090203746754</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.994318421468741</v>
+        <v>1.993482926935595</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.069072370765579</v>
+        <v>-7.070464861654156</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1360759904836835</v>
+        <v>0.1355189941282529</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.599478644465747</v>
+        <v>-1.600871135354325</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.004374176424215</v>
+        <v>2.003538681891068</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.819221976816505</v>
+        <v>-6.820614467705082</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2287582230470155</v>
+        <v>0.2282012266915849</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.599478644465747</v>
+        <v>-1.600871135354325</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.997116251407917</v>
+        <v>1.99628075687477</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.643329884349072</v>
+        <v>-6.644722375237649</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3027141835546376</v>
+        <v>0.3021571871992066</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.599478644465747</v>
+        <v>-1.600871135354325</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.000715374928566</v>
+        <v>1.999879880395419</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.471883421326608</v>
+        <v>-6.473275912215185</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.3846202748181766</v>
+        <v>0.384063278462746</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.428032181443284</v>
+        <v>-1.429424672331862</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.116910758796597</v>
+        <v>2.116075264263451</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.246850421657785</v>
+        <v>-6.248242912546362</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4736539523020027</v>
+        <v>0.4730969559465721</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.202999181774461</v>
+        <v>-1.204391672663039</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.250951036214188</v>
+        <v>2.250115541681041</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.183214679423851</v>
+        <v>-6.184607170312428</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.503803050249894</v>
+        <v>0.503246053894463</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.139363439540527</v>
+        <v>-1.140755930429105</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.293827282608866</v>
+        <v>2.292991788075719</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.139452498118009</v>
+        <v>-6.140844989006586</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.502502181556026</v>
+        <v>0.5019451852005954</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.139363439540527</v>
+        <v>-1.140755930429105</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.275021541392662</v>
+        <v>2.274186046859515</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.899022001313149</v>
+        <v>-5.900414492201726</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6004174569028478</v>
+        <v>0.5998604605474167</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.8989329427356665</v>
+        <v>-0.9003254336242443</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.421022916100455</v>
+        <v>2.420187421567308</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.826779433141954</v>
+        <v>-5.828171924030531</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6332437980061458</v>
+        <v>0.6326868016507148</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.8989329427356665</v>
+        <v>-0.9003254336242443</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.424952229935275</v>
+        <v>2.424116735402129</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.773781110860567</v>
+        <v>-5.775173601749144</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.655121710836041</v>
+        <v>0.6545647144806099</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.8435966837337276</v>
+        <v>-0.8449891746223055</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.458832569253778</v>
+        <v>2.457997074720632</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.66497622538084</v>
+        <v>-5.666368716269417</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.695641736247925</v>
+        <v>0.6950847398924944</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.8435966837337276</v>
+        <v>-0.8449891746223055</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.455830640473772</v>
+        <v>2.454995145940625</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.561394116990907</v>
+        <v>-5.446347918232406</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.7386536166145126</v>
+        <v>0.7846720961179128</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.8460571286247556</v>
+        <v>-0.7037693295543253</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.45593341054977</v>
+        <v>2.541306089992028</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.428526427927629</v>
+        <v>-5.313480229169128</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.8076948750416468</v>
+        <v>0.853713354545047</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.8460571286247556</v>
+        <v>-0.7037693295543253</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.471827593351593</v>
+        <v>2.557200272793851</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.269011324408259</v>
+        <v>-5.153965125649759</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.8726467608896966</v>
+        <v>0.9186652403930968</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.6865420251053856</v>
+        <v>-0.5442542260349553</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.568682499903517</v>
+        <v>2.654055179345775</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-5.124339179308522</v>
+        <v>-5.009292980550021</v>
       </c>
       <c r="E1932" t="n">
-        <v>0.9406037214910317</v>
+        <v>0.9866222009944319</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.5418698800056483</v>
+        <v>-0.3995820809352179</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.665573889524799</v>
+        <v>2.750946568967057</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-5.184214006666214</v>
+        <v>-5.069167807907713</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9026912819493802</v>
+        <v>0.9487097614527809</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.6017447073633404</v>
+        <v>-0.45945690829291</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.61568648451161</v>
+        <v>2.701059163953868</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-5.097414508887205</v>
+        <v>-4.982368310128704</v>
       </c>
       <c r="E1934" t="n">
-        <v>0.9598115743835502</v>
+        <v>1.00583005388695</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.6017447073633404</v>
+        <v>-0.45945690829291</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.638086977834176</v>
+        <v>2.723459657276434</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-5.099884215349011</v>
+        <v>-4.98483801659051</v>
       </c>
       <c r="E1935" t="n">
-        <v>0.9588960931722399</v>
+        <v>1.00491457267564</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.6042144138251466</v>
+        <v>-0.4619266147547162</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.636677555330504</v>
+        <v>2.722050234772762</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-5.168254401673021</v>
+        <v>-5.05320820291452</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.9425549411173377</v>
+        <v>0.9885734206207379</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.5949387147889317</v>
+        <v>-0.4526509157185012</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.653249897226935</v>
+        <v>2.738622576669193</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.276792582589155</v>
+        <v>-5.161746383830654</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.8895763773827756</v>
+        <v>0.9355948568861758</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.5949387147889317</v>
+        <v>-0.4526509157185012</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.643686605858826</v>
+        <v>2.729059285301084</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.30778574191786</v>
+        <v>-5.19273954315936</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.70188867869168</v>
+        <v>0.7479071581950807</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.5949387147889317</v>
+        <v>-0.4526509157185012</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.468396170899213</v>
+        <v>2.553768850341471</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-5.132311482125392</v>
+        <v>-5.017265283366891</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.7766456146004557</v>
+        <v>0.8226640941038559</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.5949387147889317</v>
+        <v>-0.4526509157185012</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.472963402891001</v>
+        <v>2.558336082333259</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-5.243247734766641</v>
+        <v>-5.12820153600814</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.708013142305163</v>
+        <v>0.7540316218085632</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.5949387147889317</v>
+        <v>-0.4526509157185012</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.448705431652208</v>
+        <v>2.534078111094466</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.773210297111299</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.808800045745472</v>
+        <v>2.87687430322782</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.446274312309874</v>
+        <v>-5.134397465356694</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.6299338965077754</v>
+        <v>0.8227588927713949</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.7979652923321651</v>
+        <v>-0.4588468450670553</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.330020870346174</v>
+        <v>2.601566196187587</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784343952264168</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.818972432177604</v>
+        <v>2.887046689659952</v>
       </c>
       <c r="D1942" t="n">
-        <v>-5.288348713374581</v>
+        <v>-4.9764718664214</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.7032765225140247</v>
+        <v>0.8961015187776447</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.7979652923321651</v>
+        <v>-0.4588468450670553</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.340193256778306</v>
+        <v>2.611738582619719</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.786949957742304</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.813918702751465</v>
+        <v>2.881992960233812</v>
       </c>
       <c r="D1943" t="n">
-        <v>-5.202105250348203</v>
+        <v>-4.890228403395023</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.7327201782984361</v>
+        <v>0.925545174562056</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.7979652923321651</v>
+        <v>-0.4588468450670553</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.335139527352166</v>
+        <v>2.606684853193579</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752027499316052</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.80569447819599</v>
+        <v>2.873768735678338</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.247412069747183</v>
+        <v>-4.935535222794003</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.7063732259833699</v>
+        <v>0.8991982222469896</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.8387754553413959</v>
+        <v>-0.4996570080762861</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.302429204991153</v>
+        <v>2.573974530832567</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753571165803196</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.806246351229092</v>
+        <v>2.874320608711439</v>
       </c>
       <c r="D1945" t="n">
-        <v>-5.276445174449484</v>
+        <v>-4.964568327496304</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.6953118571355508</v>
+        <v>0.8881368533991707</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.8387754553413959</v>
+        <v>-0.4996570080762861</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.302981078024255</v>
+        <v>2.574526403865668</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.733390600809503</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.735519043120457</v>
+        <v>2.803593300602805</v>
       </c>
       <c r="D1946" t="n">
-        <v>-5.183634692998624</v>
+        <v>-4.871757846045444</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.6617087416072605</v>
+        <v>0.8545337378708802</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.7459649738905365</v>
+        <v>-0.4068465266254268</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.287940058786136</v>
+        <v>2.559485384627549</v>
       </c>
     </row>
     <row r="1947">
@@ -46329,19 +46329,19 @@
         <v>3.74828581656043</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.737392519045058</v>
+        <v>2.805466776527406</v>
       </c>
       <c r="D1947" t="n">
-        <v>-5.228024162328052</v>
+        <v>-4.916147315374872</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.6458264298000902</v>
+        <v>0.8386514260637101</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.7903544432199642</v>
+        <v>-0.4512359959548544</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.26317985311308</v>
+        <v>2.534725178954494</v>
       </c>
     </row>
     <row r="1948">
@@ -46352,19 +46352,19 @@
         <v>3.721077195472742</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.732468227556781</v>
+        <v>2.800542485039129</v>
       </c>
       <c r="D1948" t="n">
-        <v>-5.115352944091802</v>
+        <v>-4.803476097138621</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.6859706256063132</v>
+        <v>0.8787956218699331</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.6776832249837139</v>
+        <v>-0.3385647777186042</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.325858292566553</v>
+        <v>2.597403618407967</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743047603798542</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.737959523387449</v>
+        <v>2.806033780869796</v>
       </c>
       <c r="D1949" t="n">
-        <v>-5.002975942909129</v>
+        <v>-4.691099095955948</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.7364127219100498</v>
+        <v>0.9292377181736695</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.6776832249837139</v>
+        <v>-0.3385647777186042</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.331349588397221</v>
+        <v>2.602894914238634</v>
       </c>
     </row>
     <row r="1950">
@@ -46398,19 +46398,19 @@
         <v>3.689597840498869</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.749456725155988</v>
+        <v>2.817530982638335</v>
       </c>
       <c r="D1950" t="n">
-        <v>-5.20121051179586</v>
+        <v>-4.889333664842679</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.6686160961238965</v>
+        <v>0.8614410923875162</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.8759177938704445</v>
+        <v>-0.5367993466053348</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.223906048833721</v>
+        <v>2.495451374675135</v>
       </c>
     </row>
     <row r="1951">
@@ -46421,19 +46421,19 @@
         <v>3.64306962170533</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.587812445156641</v>
+        <v>2.655886702638989</v>
       </c>
       <c r="D1951" t="n">
-        <v>-5.284211792821139</v>
+        <v>-4.972334945867958</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.4737713037144382</v>
+        <v>0.6665962999780579</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.8944886783976183</v>
+        <v>-0.5553702311325086</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.051119238118071</v>
+        <v>2.322664563959484</v>
       </c>
     </row>
     <row r="1952">
@@ -46444,19 +46444,19 @@
         <v>3.682716310729274</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.707962105875847</v>
+        <v>2.776036363358194</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.39282587126447</v>
+        <v>-5.080949024311289</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.5504753330563115</v>
+        <v>0.743300329319931</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.8944886783976183</v>
+        <v>-0.5553702311325086</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.171268898837276</v>
+        <v>2.442814224678689</v>
       </c>
     </row>
     <row r="1953">
@@ -46467,19 +46467,19 @@
         <v>3.733012441190773</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.722475131978169</v>
+        <v>2.790549389460517</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.479424454245573</v>
+        <v>-5.167547607292392</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.5303489259661931</v>
+        <v>0.723173922229813</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.8944886783976183</v>
+        <v>-0.5553702311325086</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.185781924939599</v>
+        <v>2.457327250781012</v>
       </c>
     </row>
     <row r="1954">
@@ -46490,19 +46490,19 @@
         <v>3.741174069913429</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.719894573320538</v>
+        <v>2.787968830802886</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.441040791687421</v>
+        <v>-5.129163944734241</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.5431218323318223</v>
+        <v>0.7359468285954422</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.8561050158394671</v>
+        <v>-0.5169865685743574</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.206231563816858</v>
+        <v>2.477776889658272</v>
       </c>
     </row>
     <row r="1955">
@@ -46513,19 +46513,19 @@
         <v>3.751147197532489</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.71662360216584</v>
+        <v>2.784697859648188</v>
       </c>
       <c r="D1955" t="n">
-        <v>-5.263924461652255</v>
+        <v>-4.952047614699075</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.6106973931911908</v>
+        <v>0.8035223894548105</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.8561050158394671</v>
+        <v>-0.5169865685743574</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.20296059266216</v>
+        <v>2.474505918503574</v>
       </c>
     </row>
     <row r="1956">
@@ -46536,19 +46536,19 @@
         <v>3.741328448793906</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.717306993927753</v>
+        <v>2.785381251410101</v>
       </c>
       <c r="D1956" t="n">
-        <v>-5.309016706485801</v>
+        <v>-4.997139859532621</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.5933438870196857</v>
+        <v>0.7861688832833051</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.9180010590088569</v>
+        <v>-0.5788826117437472</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.166506358522439</v>
+        <v>2.438051684363853</v>
       </c>
     </row>
     <row r="1957">
@@ -46559,19 +46559,19 @@
         <v>3.75072937701124</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.711093969234168</v>
+        <v>2.779168226716515</v>
       </c>
       <c r="D1957" t="n">
-        <v>-5.129641285247033</v>
+        <v>-4.817764438293853</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.6588810308216071</v>
+        <v>0.8517060270852266</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.7612243008381382</v>
+        <v>-0.4221058535730285</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.254359388731285</v>
+        <v>2.525904714572698</v>
       </c>
     </row>
     <row r="1958">
@@ -46582,19 +46582,19 @@
         <v>3.716991718982235</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.691901424565757</v>
+        <v>2.759975682048105</v>
       </c>
       <c r="D1958" t="n">
-        <v>-5.17465549876764</v>
+        <v>-4.862778651814459</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.6216828007449542</v>
+        <v>0.8145077970085741</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.7915731961527428</v>
+        <v>-0.4524547488876332</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.216957506874112</v>
+        <v>2.488502832715525</v>
       </c>
     </row>
     <row r="1959">
@@ -46605,19 +46605,19 @@
         <v>3.737026608509541</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.697592986904703</v>
+        <v>2.765667244387051</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.441660009040075</v>
+        <v>-5.129783162086894</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.5205725589749259</v>
+        <v>0.7133975552385459</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.9859362341956914</v>
+        <v>-0.6468177869305818</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.106031246387289</v>
+        <v>2.377576572228702</v>
       </c>
     </row>
     <row r="1960">
@@ -46628,19 +46628,19 @@
         <v>3.702309454760815</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.696796908801204</v>
+        <v>2.764871166283552</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.542857790477248</v>
+        <v>-5.230980943524067</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.479297368296558</v>
+        <v>0.6721223645601784</v>
       </c>
       <c r="F1960" t="n">
-        <v>-1.054345047741011</v>
+        <v>-0.7152266004759009</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.064189880156599</v>
+        <v>2.335735205998012</v>
       </c>
     </row>
     <row r="1961">
@@ -46651,19 +46651,19 @@
         <v>3.705571661815461</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.694396870355521</v>
+        <v>2.762471127837869</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.510382204306476</v>
+        <v>-5.198505357353294</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.4898875643191838</v>
+        <v>0.6827125605828037</v>
       </c>
       <c r="F1961" t="n">
-        <v>-1.054345047741011</v>
+        <v>-0.7152266004759009</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.061789841710915</v>
+        <v>2.333335167552329</v>
       </c>
     </row>
     <row r="1962">
@@ -46674,19 +46674,19 @@
         <v>3.709510443378106</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.690921589563766</v>
+        <v>2.758995847046114</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.491344076599178</v>
+        <v>-5.179467229645997</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.4940275346103475</v>
+        <v>0.6868525308739675</v>
       </c>
       <c r="F1962" t="n">
-        <v>-1.112528659072205</v>
+        <v>-0.7734102118070955</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.023404394120444</v>
+        <v>2.294949719961857</v>
       </c>
     </row>
     <row r="1963">
@@ -46697,19 +46697,19 @@
         <v>3.731064473131256</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.868503458502447</v>
+        <v>2.936577715984794</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.522470707749797</v>
+        <v>-5.210593860796616</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.6591587510887806</v>
+        <v>0.851983747352401</v>
       </c>
       <c r="F1963" t="n">
-        <v>-1.112528659072205</v>
+        <v>-0.7734102118070955</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.200986263059124</v>
+        <v>2.472531588900537</v>
       </c>
     </row>
     <row r="1964">
@@ -46720,19 +46720,19 @@
         <v>3.722447362067872</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.86933678748858</v>
+        <v>2.937411044970928</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.574791088350588</v>
+        <v>-5.262914241397407</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.6390639278345978</v>
+        <v>0.8318889240982177</v>
       </c>
       <c r="F1964" t="n">
-        <v>-1.077581799063333</v>
+        <v>-0.7384633517982233</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.222787708050581</v>
+        <v>2.494333033891994</v>
       </c>
     </row>
     <row r="1965">
@@ -46743,19 +46743,19 @@
         <v>3.787425580789129</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.875345317885506</v>
+        <v>2.943419575367854</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.595048386879546</v>
+        <v>-5.283171539926365</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.6369695388199403</v>
+        <v>0.8297945350835603</v>
       </c>
       <c r="F1965" t="n">
-        <v>-1.077581799063333</v>
+        <v>-0.7384633517982233</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.228796238447507</v>
+        <v>2.50034156428892</v>
       </c>
     </row>
     <row r="1966">
@@ -46766,19 +46766,19 @@
         <v>3.781501250519914</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.954497965677528</v>
+        <v>3.022572223159876</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.447305416644544</v>
+        <v>-5.135428569691363</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.7752193747059635</v>
+        <v>0.9680443709695834</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.9097744418284498</v>
+        <v>-0.5706559945633402</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.408633300580459</v>
+        <v>2.680178626421872</v>
       </c>
     </row>
     <row r="1967">
@@ -46789,19 +46789,19 @@
         <v>3.802245929181177</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.957291587209009</v>
+        <v>3.025365844691357</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.549320099175765</v>
+        <v>-5.237443252222584</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.7372071232249557</v>
+        <v>0.9300321194885757</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.9097744418284498</v>
+        <v>-0.5706559945633402</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.41142692211194</v>
+        <v>2.682972247953353</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.805608985394735</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.957953935600667</v>
+        <v>3.026028193083015</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.543167393122981</v>
+        <v>-5.2312905461698</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.7403305540377279</v>
+        <v>0.9331555503013478</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.9036217357756655</v>
+        <v>-0.5645032885105559</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.415780894135269</v>
+        <v>2.687326219976682</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890617</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.957034412340778</v>
+        <v>3.025108669823125</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.685932725945631</v>
+        <v>-5.37405587899245</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.6823048976487782</v>
+        <v>0.8751298939123981</v>
       </c>
       <c r="F1969" t="n">
-        <v>-1.046387068598316</v>
+        <v>-0.7072686213332062</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.329202171181789</v>
+        <v>2.600747497023202</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798432</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.023369966137599</v>
+        <v>3.091444223619946</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.623634727169509</v>
+        <v>-5.311757880216327</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.7735596509560478</v>
+        <v>0.9663846472196678</v>
       </c>
       <c r="F1970" t="n">
-        <v>-1.046387068598316</v>
+        <v>-0.7072686213332062</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.39553772497861</v>
+        <v>2.667083050820023</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992196</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.731950838526997</v>
+        <v>2.800025096009344</v>
       </c>
       <c r="D1971" t="n">
-        <v>-5.421844529504351</v>
+        <v>-5.10996768255117</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.5628566024115091</v>
+        <v>0.7556815986751291</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.8483688764291615</v>
+        <v>-0.5092504291640518</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.2229295126695</v>
+        <v>2.494474838510913</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852428</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.802241070849172</v>
+        <v>2.870315328331519</v>
       </c>
       <c r="D1972" t="n">
-        <v>-5.361953847861757</v>
+        <v>-5.050077000908576</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.6571031073907214</v>
+        <v>0.8499281036543418</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.788478194786568</v>
+        <v>-0.4493597475214584</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.329154153977231</v>
+        <v>2.600699479818645</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.81906330031955</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.816868806965215</v>
+        <v>2.884943064447563</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.459694392486732</v>
+        <v>-5.147817545533551</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.6326346256567756</v>
+        <v>0.8254596219203956</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.8043674729195482</v>
+        <v>-0.4652490256544385</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.334248323213487</v>
+        <v>2.6057936490549</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489388</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.815404787789887</v>
+        <v>2.883479045272235</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.636032152609661</v>
+        <v>-5.32415530565648</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.5606355024322753</v>
+        <v>0.7534604986958957</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.9807052330424777</v>
+        <v>-0.6415867857773679</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.226981647964401</v>
+        <v>2.498526973805814</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397798</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.813896405829816</v>
+        <v>2.881970663312163</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.635342780448438</v>
+        <v>-5.323465933495257</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.5594028693366933</v>
+        <v>0.7522278656003132</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.9807052330424777</v>
+        <v>-0.6415867857773679</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.22547326600433</v>
+        <v>2.497018591845743</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.836023391024966</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.813759273265252</v>
+        <v>2.8818335307476</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.641913745503031</v>
+        <v>-5.330036898549849</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.5566373507502922</v>
+        <v>0.7494623470139126</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.9872761980970706</v>
+        <v>-0.6481577508319609</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.22139355440701</v>
+        <v>2.492938880248423</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821591150863229</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.813759273265252</v>
+        <v>2.8818335307476</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.633959775208258</v>
+        <v>-5.322082928255077</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.5598189388682013</v>
+        <v>0.7526439351318213</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.9872761980970706</v>
+        <v>-0.6481577508319609</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.22139355440701</v>
+        <v>2.492938880248423</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833040181947588</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.820141030293057</v>
+        <v>2.888215287775404</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.623586398875172</v>
+        <v>-5.31170955192199</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.5703500464292408</v>
+        <v>0.7631750426928607</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.9769028217639832</v>
+        <v>-0.6377843744988736</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.233999337234667</v>
+        <v>2.50554466307608</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822707244326881</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.825033403667781</v>
+        <v>2.893107661150129</v>
       </c>
       <c r="D1979" t="n">
-        <v>-5.495902089080875</v>
+        <v>-5.184025242127694</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.626316143721684</v>
+        <v>0.8191411399853039</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.8492185119696868</v>
+        <v>-0.5101000647045771</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.31550229648597</v>
+        <v>2.587047622327383</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828837911314556</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.811788076143654</v>
+        <v>2.879862333626001</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.556568679483265</v>
+        <v>-5.244691832530084</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.5888041800366004</v>
+        <v>0.7816291763002203</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.9309168286882205</v>
+        <v>-0.5917983814231108</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.253237978930722</v>
+        <v>2.524783304772135</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816866067690031</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.815885778754282</v>
+        <v>2.88396003623663</v>
       </c>
       <c r="D1981" t="n">
-        <v>-5.491574819549619</v>
+        <v>-5.179697972596438</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.6188994266206871</v>
+        <v>0.8117244228843075</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.9040862140840651</v>
+        <v>-0.5649677668189554</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.273434050303844</v>
+        <v>2.544979376145257</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817961388674314</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.82004671838536</v>
+        <v>2.888120975867708</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.592333455306617</v>
+        <v>-5.280456608353436</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.5827569119489659</v>
+        <v>0.7755819082125859</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.9929117828110705</v>
+        <v>-0.6537933355459609</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.224299648698718</v>
+        <v>2.495844974540132</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.826713779163224</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.825926320913197</v>
+        <v>2.894000578395545</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.548130618220717</v>
+        <v>-5.236253771267536</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.6063176493111633</v>
+        <v>0.7991426455747832</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.9487089457251701</v>
+        <v>-0.6095904984600604</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.256700953478096</v>
+        <v>2.528246279319509</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838228663022909</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.824336321382445</v>
+        <v>2.892410578864792</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.58510964588416</v>
+        <v>-5.273232798930978</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.5899360387150336</v>
+        <v>0.782761034978654</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.9117350439338395</v>
+        <v>-0.5726165966687299</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.277295295022141</v>
+        <v>2.548840620863555</v>
       </c>
     </row>
     <row r="1985">
@@ -47203,19 +47203,19 @@
         <v>3.863924114042143</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.875584086565484</v>
+        <v>2.943658344047832</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.605167724749</v>
+        <v>-5.293290877795819</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.633160572352137</v>
+        <v>0.8259855686157573</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.9117350439338395</v>
+        <v>-0.5726165966687299</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.328543060205181</v>
+        <v>2.600088386046595</v>
       </c>
     </row>
     <row r="1986">
@@ -47226,19 +47226,19 @@
         <v>3.865367715078284</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.874024791159738</v>
+        <v>2.942099048642085</v>
       </c>
       <c r="D1986" t="n">
-        <v>-5.56523705157111</v>
+        <v>-5.253360204617929</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.6475735462175463</v>
+        <v>0.8403985424811666</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.8718043707559492</v>
+        <v>-0.5326859234908395</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.350942168706168</v>
+        <v>2.622487494547582</v>
       </c>
     </row>
     <row r="1987">
@@ -47249,19 +47249,19 @@
         <v>3.8645188762324</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.868973019398008</v>
+        <v>2.937047276880355</v>
       </c>
       <c r="D1987" t="n">
-        <v>-5.524766704008405</v>
+        <v>-5.212889857055224</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.6587099134808985</v>
+        <v>0.8515349097445184</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.8313340231932442</v>
+        <v>-0.4922155759281346</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.370172605482062</v>
+        <v>2.641717931323475</v>
       </c>
     </row>
     <row r="1988">
@@ -47272,19 +47272,19 @@
         <v>3.842576394162115</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.886160423490713</v>
+        <v>2.95423468097306</v>
       </c>
       <c r="D1988" t="n">
-        <v>-5.4595425228812</v>
+        <v>-5.147665675928018</v>
       </c>
       <c r="E1988" t="n">
-        <v>0.7019869900244853</v>
+        <v>0.8948119862881057</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.7661098420660386</v>
+        <v>-0.426991394800929</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.42649451825109</v>
+        <v>2.698039844092503</v>
       </c>
     </row>
     <row r="1989">
@@ -47295,19 +47295,19 @@
         <v>3.84009022063982</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.882121395789993</v>
+        <v>2.950195653272341</v>
       </c>
       <c r="D1989" t="n">
-        <v>-5.510036813238256</v>
+        <v>-5.198159966285075</v>
       </c>
       <c r="E1989" t="n">
-        <v>0.6777502461809433</v>
+        <v>0.8705752424445636</v>
       </c>
       <c r="F1989" t="n">
-        <v>-0.8111305791921128</v>
+        <v>-0.4720121319270032</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.395443048274726</v>
+        <v>2.666988374116139</v>
       </c>
     </row>
     <row r="1990">
@@ -47318,19 +47318,19 @@
         <v>3.845198842749923</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.883378188121233</v>
+        <v>2.951452445603581</v>
       </c>
       <c r="D1990" t="n">
-        <v>-5.530148469272964</v>
+        <v>-5.218271622319783</v>
       </c>
       <c r="E1990" t="n">
-        <v>0.6709623760983003</v>
+        <v>0.8637873723619203</v>
       </c>
       <c r="F1990" t="n">
-        <v>-0.8001032341946936</v>
+        <v>-0.460984786929584</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.403316247604418</v>
+        <v>2.674861573445831</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.813580557712028</v>
+        <v>3.871613373327457</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.878744993712149</v>
+        <v>2.895407856400374</v>
       </c>
       <c r="D1991" t="n">
-        <v>-5.547461440927848</v>
+        <v>-5.425730735971747</v>
       </c>
       <c r="E1991" t="n">
-        <v>0.6594039930272624</v>
+        <v>0.7247591376979279</v>
       </c>
       <c r="F1991" t="n">
-        <v>-0.7847417403392911</v>
+        <v>-0.6547370502948218</v>
       </c>
       <c r="G1991" t="n">
-        <v>2.407899949508574</v>
+        <v>2.502565626223482</v>
       </c>
     </row>
   </sheetData>
